--- a/Backtest_Saldo_Menor_EH2_TOP2_ODDREAL_2026.xlsx
+++ b/Backtest_Saldo_Menor_EH2_TOP2_ODDREAL_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S472"/>
+  <dimension ref="A1:S502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1959,44 +1959,44 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FRANCE 4</t>
+          <t>SPAIN 3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>GOAL FC</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Lugo</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Lugo</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>GOAL FC</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0.8</v>
+        <v>1.11</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -2917,27 +2917,27 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tanta</t>
+          <t>Aswan SC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Baladiyat El Mahalla</t>
+          <t>Proxy</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Baladiyat El Mahalla</t>
+          <t>Proxy</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tanta</t>
+          <t>Aswan SC</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -2952,27 +2952,27 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>0.0669</v>
+        <v>-1</v>
       </c>
       <c r="P32" t="n">
-        <v>6.69</v>
+        <v>-100</v>
       </c>
       <c r="Q32" t="n">
-        <v>-1.433</v>
+        <v>-2.5</v>
       </c>
       <c r="R32" t="n">
-        <v>-143.3</v>
+        <v>-250</v>
       </c>
       <c r="S32" t="n">
-        <v>90.3</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -3045,13 +3045,13 @@
         <v>4.78</v>
       </c>
       <c r="Q33" t="n">
-        <v>-1.385</v>
+        <v>-2.452</v>
       </c>
       <c r="R33" t="n">
-        <v>-138.5</v>
+        <v>-245.2</v>
       </c>
       <c r="S33" t="n">
-        <v>90.59999999999999</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="34">
@@ -3124,13 +3124,13 @@
         <v>4.78</v>
       </c>
       <c r="Q34" t="n">
-        <v>-1.338</v>
+        <v>-2.405</v>
       </c>
       <c r="R34" t="n">
-        <v>-133.8</v>
+        <v>-240.5</v>
       </c>
       <c r="S34" t="n">
-        <v>90.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -3203,13 +3203,13 @@
         <v>4.78</v>
       </c>
       <c r="Q35" t="n">
-        <v>-1.29</v>
+        <v>-2.357</v>
       </c>
       <c r="R35" t="n">
-        <v>-129</v>
+        <v>-235.7</v>
       </c>
       <c r="S35" t="n">
-        <v>91.2</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="36">
@@ -3282,13 +3282,13 @@
         <v>5.73</v>
       </c>
       <c r="Q36" t="n">
-        <v>-1.233</v>
+        <v>-2.299</v>
       </c>
       <c r="R36" t="n">
-        <v>-123.3</v>
+        <v>-229.9</v>
       </c>
       <c r="S36" t="n">
-        <v>91.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3361,13 +3361,13 @@
         <v>3.82</v>
       </c>
       <c r="Q37" t="n">
-        <v>-1.194</v>
+        <v>-2.261</v>
       </c>
       <c r="R37" t="n">
-        <v>-119.4</v>
+        <v>-226.1</v>
       </c>
       <c r="S37" t="n">
-        <v>91.7</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -3440,13 +3440,13 @@
         <v>5.73</v>
       </c>
       <c r="Q38" t="n">
-        <v>-1.137</v>
+        <v>-2.204</v>
       </c>
       <c r="R38" t="n">
-        <v>-113.7</v>
+        <v>-220.4</v>
       </c>
       <c r="S38" t="n">
-        <v>91.90000000000001</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="39">
@@ -3519,13 +3519,13 @@
         <v>6.69</v>
       </c>
       <c r="Q39" t="n">
-        <v>-1.07</v>
+        <v>-2.137</v>
       </c>
       <c r="R39" t="n">
-        <v>-107</v>
+        <v>-213.7</v>
       </c>
       <c r="S39" t="n">
-        <v>92.09999999999999</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="40">
@@ -3598,13 +3598,13 @@
         <v>3.82</v>
       </c>
       <c r="Q40" t="n">
-        <v>-1.032</v>
+        <v>-2.099</v>
       </c>
       <c r="R40" t="n">
-        <v>-103.2</v>
+        <v>-209.9</v>
       </c>
       <c r="S40" t="n">
-        <v>92.3</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="41">
@@ -3677,13 +3677,13 @@
         <v>8.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.946</v>
+        <v>-2.013</v>
       </c>
       <c r="R41" t="n">
-        <v>-94.59999999999999</v>
+        <v>-201.3</v>
       </c>
       <c r="S41" t="n">
-        <v>92.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42">
@@ -3756,13 +3756,13 @@
         <v>9.550000000000001</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.85</v>
+        <v>-1.917</v>
       </c>
       <c r="R42" t="n">
-        <v>-85</v>
+        <v>-191.7</v>
       </c>
       <c r="S42" t="n">
-        <v>92.7</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="43">
@@ -3835,13 +3835,13 @@
         <v>4.78</v>
       </c>
       <c r="Q43" t="n">
-        <v>-0.803</v>
+        <v>-1.87</v>
       </c>
       <c r="R43" t="n">
-        <v>-80.3</v>
+        <v>-187</v>
       </c>
       <c r="S43" t="n">
-        <v>92.90000000000001</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="44">
@@ -3914,13 +3914,13 @@
         <v>3.82</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.764</v>
+        <v>-1.831</v>
       </c>
       <c r="R44" t="n">
-        <v>-76.40000000000001</v>
+        <v>-183.1</v>
       </c>
       <c r="S44" t="n">
-        <v>93</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="45">
@@ -3993,13 +3993,13 @@
         <v>4.78</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.717</v>
+        <v>-1.784</v>
       </c>
       <c r="R45" t="n">
-        <v>-71.7</v>
+        <v>-178.4</v>
       </c>
       <c r="S45" t="n">
-        <v>93.2</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -4072,13 +4072,13 @@
         <v>7.64</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.64</v>
+        <v>-1.707</v>
       </c>
       <c r="R46" t="n">
-        <v>-64</v>
+        <v>-170.7</v>
       </c>
       <c r="S46" t="n">
-        <v>93.3</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -4151,13 +4151,13 @@
         <v>4.78</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.592</v>
+        <v>-1.659</v>
       </c>
       <c r="R47" t="n">
-        <v>-59.2</v>
+        <v>-165.9</v>
       </c>
       <c r="S47" t="n">
-        <v>93.5</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="48">
@@ -4230,13 +4230,13 @@
         <v>2.87</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-1.631</v>
       </c>
       <c r="R48" t="n">
-        <v>-56.4</v>
+        <v>-163.1</v>
       </c>
       <c r="S48" t="n">
-        <v>93.59999999999999</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="49">
@@ -4309,13 +4309,13 @@
         <v>4.78</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.516</v>
+        <v>-1.583</v>
       </c>
       <c r="R49" t="n">
-        <v>-51.6</v>
+        <v>-158.3</v>
       </c>
       <c r="S49" t="n">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="50">
@@ -4388,13 +4388,13 @@
         <v>4.78</v>
       </c>
       <c r="Q50" t="n">
-        <v>-0.468</v>
+        <v>-1.535</v>
       </c>
       <c r="R50" t="n">
-        <v>-46.8</v>
+        <v>-153.5</v>
       </c>
       <c r="S50" t="n">
-        <v>93.90000000000001</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="51">
@@ -4467,13 +4467,13 @@
         <v>2.87</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.44</v>
+        <v>-1.506</v>
       </c>
       <c r="R51" t="n">
-        <v>-44</v>
+        <v>-150.6</v>
       </c>
       <c r="S51" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="52">
@@ -4546,13 +4546,13 @@
         <v>3.82</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.401</v>
+        <v>-1.468</v>
       </c>
       <c r="R52" t="n">
-        <v>-40.1</v>
+        <v>-146.8</v>
       </c>
       <c r="S52" t="n">
-        <v>94.09999999999999</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="53">
@@ -4625,13 +4625,13 @@
         <v>7.64</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.325</v>
+        <v>-1.392</v>
       </c>
       <c r="R53" t="n">
-        <v>-32.5</v>
+        <v>-139.2</v>
       </c>
       <c r="S53" t="n">
-        <v>94.2</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="54">
@@ -4704,13 +4704,13 @@
         <v>8.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>-0.239</v>
+        <v>-1.306</v>
       </c>
       <c r="R54" t="n">
-        <v>-23.9</v>
+        <v>-130.6</v>
       </c>
       <c r="S54" t="n">
-        <v>94.3</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="55">
@@ -4783,13 +4783,13 @@
         <v>3.82</v>
       </c>
       <c r="Q55" t="n">
-        <v>-0.201</v>
+        <v>-1.268</v>
       </c>
       <c r="R55" t="n">
-        <v>-20.1</v>
+        <v>-126.8</v>
       </c>
       <c r="S55" t="n">
-        <v>94.40000000000001</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -4862,13 +4862,13 @@
         <v>2.87</v>
       </c>
       <c r="Q56" t="n">
-        <v>-0.172</v>
+        <v>-1.239</v>
       </c>
       <c r="R56" t="n">
-        <v>-17.2</v>
+        <v>-123.9</v>
       </c>
       <c r="S56" t="n">
-        <v>94.5</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="57">
@@ -4941,13 +4941,13 @@
         <v>7.64</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.096</v>
+        <v>-1.162</v>
       </c>
       <c r="R57" t="n">
-        <v>-9.6</v>
+        <v>-116.2</v>
       </c>
       <c r="S57" t="n">
-        <v>94.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="58">
@@ -5020,13 +5020,13 @@
         <v>4.78</v>
       </c>
       <c r="Q58" t="n">
-        <v>-0.048</v>
+        <v>-1.115</v>
       </c>
       <c r="R58" t="n">
-        <v>-4.8</v>
+        <v>-111.5</v>
       </c>
       <c r="S58" t="n">
-        <v>94.7</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59">
@@ -5099,13 +5099,13 @@
         <v>6.69</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.019</v>
+        <v>-1.048</v>
       </c>
       <c r="R59" t="n">
-        <v>1.9</v>
+        <v>-104.8</v>
       </c>
       <c r="S59" t="n">
-        <v>94.8</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -5129,27 +5129,27 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aswan SC</t>
+          <t>Al-Sekka</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>WE SC</t>
+          <t>Asyut Petroleum</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>WE SC</t>
+          <t>Asyut Petroleum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Aswan SC</t>
+          <t>Al-Sekka</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -5164,27 +5164,27 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="O60" t="n">
-        <v>0.0669</v>
+        <v>-1</v>
       </c>
       <c r="P60" t="n">
-        <v>6.69</v>
+        <v>-100</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.08599999999999999</v>
+        <v>-2.048</v>
       </c>
       <c r="R60" t="n">
-        <v>8.6</v>
+        <v>-204.8</v>
       </c>
       <c r="S60" t="n">
-        <v>94.90000000000001</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="61">
@@ -5208,27 +5208,27 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al-Sekka</t>
+          <t>Aswan SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Asyut Petroleum</t>
+          <t>WE SC</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Asyut Petroleum</t>
+          <t>WE SC</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Al-Sekka</t>
+          <t>Aswan SC</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -5243,27 +5243,27 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="O61" t="n">
-        <v>-1</v>
+        <v>0.0669</v>
       </c>
       <c r="P61" t="n">
-        <v>-100</v>
+        <v>6.69</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.914</v>
+        <v>-1.981</v>
       </c>
       <c r="R61" t="n">
-        <v>-91.40000000000001</v>
+        <v>-198.1</v>
       </c>
       <c r="S61" t="n">
-        <v>93.3</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="62">
@@ -5336,13 +5336,13 @@
         <v>6.69</v>
       </c>
       <c r="Q62" t="n">
-        <v>-0.847</v>
+        <v>-1.914</v>
       </c>
       <c r="R62" t="n">
-        <v>-84.7</v>
+        <v>-191.4</v>
       </c>
       <c r="S62" t="n">
-        <v>93.40000000000001</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="63">
@@ -5415,13 +5415,13 @@
         <v>8.6</v>
       </c>
       <c r="Q63" t="n">
-        <v>-0.761</v>
+        <v>-1.828</v>
       </c>
       <c r="R63" t="n">
-        <v>-76.09999999999999</v>
+        <v>-182.8</v>
       </c>
       <c r="S63" t="n">
-        <v>93.5</v>
+        <v>91.90000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -5494,13 +5494,13 @@
         <v>4.78</v>
       </c>
       <c r="Q64" t="n">
-        <v>-0.713</v>
+        <v>-1.78</v>
       </c>
       <c r="R64" t="n">
-        <v>-71.3</v>
+        <v>-178</v>
       </c>
       <c r="S64" t="n">
-        <v>93.7</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -5573,13 +5573,13 @@
         <v>8.6</v>
       </c>
       <c r="Q65" t="n">
-        <v>-0.627</v>
+        <v>-1.694</v>
       </c>
       <c r="R65" t="n">
-        <v>-62.7</v>
+        <v>-169.4</v>
       </c>
       <c r="S65" t="n">
-        <v>93.8</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="66">
@@ -5652,13 +5652,13 @@
         <v>3.82</v>
       </c>
       <c r="Q66" t="n">
-        <v>-0.589</v>
+        <v>-1.656</v>
       </c>
       <c r="R66" t="n">
-        <v>-58.9</v>
+        <v>-165.6</v>
       </c>
       <c r="S66" t="n">
-        <v>93.8</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="67">
@@ -5731,13 +5731,13 @@
         <v>-100</v>
       </c>
       <c r="Q67" t="n">
-        <v>-1.589</v>
+        <v>-2.656</v>
       </c>
       <c r="R67" t="n">
-        <v>-158.9</v>
+        <v>-265.6</v>
       </c>
       <c r="S67" t="n">
-        <v>92.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -5810,13 +5810,13 @@
         <v>6.69</v>
       </c>
       <c r="Q68" t="n">
-        <v>-1.522</v>
+        <v>-2.589</v>
       </c>
       <c r="R68" t="n">
-        <v>-152.2</v>
+        <v>-258.9</v>
       </c>
       <c r="S68" t="n">
-        <v>92.5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="69">
@@ -5889,13 +5889,13 @@
         <v>-100</v>
       </c>
       <c r="Q69" t="n">
-        <v>-2.522</v>
+        <v>-3.589</v>
       </c>
       <c r="R69" t="n">
-        <v>-252.2</v>
+        <v>-358.9</v>
       </c>
       <c r="S69" t="n">
-        <v>91.2</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="70">
@@ -5968,13 +5968,13 @@
         <v>8.6</v>
       </c>
       <c r="Q70" t="n">
-        <v>-2.436</v>
+        <v>-3.503</v>
       </c>
       <c r="R70" t="n">
-        <v>-243.6</v>
+        <v>-350.3</v>
       </c>
       <c r="S70" t="n">
-        <v>91.3</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -6047,13 +6047,13 @@
         <v>2.87</v>
       </c>
       <c r="Q71" t="n">
-        <v>-2.408</v>
+        <v>-3.474</v>
       </c>
       <c r="R71" t="n">
-        <v>-240.8</v>
+        <v>-347.4</v>
       </c>
       <c r="S71" t="n">
-        <v>91.40000000000001</v>
+        <v>90</v>
       </c>
     </row>
     <row r="72">
@@ -6126,13 +6126,13 @@
         <v>-100</v>
       </c>
       <c r="Q72" t="n">
-        <v>-3.408</v>
+        <v>-4.474</v>
       </c>
       <c r="R72" t="n">
-        <v>-340.8</v>
+        <v>-447.4</v>
       </c>
       <c r="S72" t="n">
-        <v>90.09999999999999</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="73">
@@ -6205,13 +6205,13 @@
         <v>6.69</v>
       </c>
       <c r="Q73" t="n">
-        <v>-3.341</v>
+        <v>-4.407</v>
       </c>
       <c r="R73" t="n">
-        <v>-334.1</v>
+        <v>-440.7</v>
       </c>
       <c r="S73" t="n">
-        <v>90.3</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="74">
@@ -6284,13 +6284,13 @@
         <v>6.69</v>
       </c>
       <c r="Q74" t="n">
-        <v>-3.274</v>
+        <v>-4.341</v>
       </c>
       <c r="R74" t="n">
-        <v>-327.4</v>
+        <v>-434.1</v>
       </c>
       <c r="S74" t="n">
-        <v>90.40000000000001</v>
+        <v>89</v>
       </c>
     </row>
     <row r="75">
@@ -6363,13 +6363,13 @@
         <v>5.73</v>
       </c>
       <c r="Q75" t="n">
-        <v>-3.216</v>
+        <v>-4.283</v>
       </c>
       <c r="R75" t="n">
-        <v>-321.6</v>
+        <v>-428.3</v>
       </c>
       <c r="S75" t="n">
-        <v>90.5</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="76">
@@ -6442,13 +6442,13 @@
         <v>3.82</v>
       </c>
       <c r="Q76" t="n">
-        <v>-3.178</v>
+        <v>-4.245</v>
       </c>
       <c r="R76" t="n">
-        <v>-317.8</v>
+        <v>-424.5</v>
       </c>
       <c r="S76" t="n">
-        <v>90.7</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="77">
@@ -6521,13 +6521,13 @@
         <v>2.87</v>
       </c>
       <c r="Q77" t="n">
-        <v>-3.15</v>
+        <v>-4.216</v>
       </c>
       <c r="R77" t="n">
-        <v>-315</v>
+        <v>-421.6</v>
       </c>
       <c r="S77" t="n">
-        <v>90.8</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="78">
@@ -6600,13 +6600,13 @@
         <v>-100</v>
       </c>
       <c r="Q78" t="n">
-        <v>-4.15</v>
+        <v>-5.216</v>
       </c>
       <c r="R78" t="n">
-        <v>-415</v>
+        <v>-521.6</v>
       </c>
       <c r="S78" t="n">
-        <v>89.59999999999999</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="79">
@@ -6679,13 +6679,13 @@
         <v>6.69</v>
       </c>
       <c r="Q79" t="n">
-        <v>-4.083</v>
+        <v>-5.149</v>
       </c>
       <c r="R79" t="n">
-        <v>-408.3</v>
+        <v>-514.9</v>
       </c>
       <c r="S79" t="n">
-        <v>89.7</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="80">
@@ -6758,13 +6758,13 @@
         <v>4.78</v>
       </c>
       <c r="Q80" t="n">
-        <v>-4.035</v>
+        <v>-5.102</v>
       </c>
       <c r="R80" t="n">
-        <v>-403.5</v>
+        <v>-510.2</v>
       </c>
       <c r="S80" t="n">
-        <v>89.90000000000001</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -6837,13 +6837,13 @@
         <v>5.73</v>
       </c>
       <c r="Q81" t="n">
-        <v>-3.977</v>
+        <v>-5.044</v>
       </c>
       <c r="R81" t="n">
-        <v>-397.7</v>
+        <v>-504.4</v>
       </c>
       <c r="S81" t="n">
-        <v>90</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="82">
@@ -6916,13 +6916,13 @@
         <v>4.78</v>
       </c>
       <c r="Q82" t="n">
-        <v>-3.93</v>
+        <v>-4.997</v>
       </c>
       <c r="R82" t="n">
-        <v>-393</v>
+        <v>-499.7</v>
       </c>
       <c r="S82" t="n">
-        <v>90.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -6995,13 +6995,13 @@
         <v>6.69</v>
       </c>
       <c r="Q83" t="n">
-        <v>-3.863</v>
+        <v>-4.93</v>
       </c>
       <c r="R83" t="n">
-        <v>-386.3</v>
+        <v>-493</v>
       </c>
       <c r="S83" t="n">
-        <v>90.2</v>
+        <v>89</v>
       </c>
     </row>
     <row r="84">
@@ -7074,13 +7074,13 @@
         <v>3.82</v>
       </c>
       <c r="Q84" t="n">
-        <v>-3.825</v>
+        <v>-4.892</v>
       </c>
       <c r="R84" t="n">
-        <v>-382.5</v>
+        <v>-489.2</v>
       </c>
       <c r="S84" t="n">
-        <v>90.40000000000001</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="85">
@@ -7153,13 +7153,13 @@
         <v>7.64</v>
       </c>
       <c r="Q85" t="n">
-        <v>-3.748</v>
+        <v>-4.815</v>
       </c>
       <c r="R85" t="n">
-        <v>-374.8</v>
+        <v>-481.5</v>
       </c>
       <c r="S85" t="n">
-        <v>90.5</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="86">
@@ -7232,13 +7232,13 @@
         <v>4.78</v>
       </c>
       <c r="Q86" t="n">
-        <v>-3.7</v>
+        <v>-4.767</v>
       </c>
       <c r="R86" t="n">
-        <v>-370</v>
+        <v>-476.7</v>
       </c>
       <c r="S86" t="n">
-        <v>90.59999999999999</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="87">
@@ -7311,13 +7311,13 @@
         <v>6.69</v>
       </c>
       <c r="Q87" t="n">
-        <v>-3.633</v>
+        <v>-4.7</v>
       </c>
       <c r="R87" t="n">
-        <v>-363.3</v>
+        <v>-470</v>
       </c>
       <c r="S87" t="n">
-        <v>90.7</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="88">
@@ -7390,13 +7390,13 @@
         <v>3.82</v>
       </c>
       <c r="Q88" t="n">
-        <v>-3.595</v>
+        <v>-4.662</v>
       </c>
       <c r="R88" t="n">
-        <v>-359.5</v>
+        <v>-466.2</v>
       </c>
       <c r="S88" t="n">
-        <v>90.8</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="89">
@@ -7469,13 +7469,13 @@
         <v>3.82</v>
       </c>
       <c r="Q89" t="n">
-        <v>-3.557</v>
+        <v>-4.624</v>
       </c>
       <c r="R89" t="n">
-        <v>-355.7</v>
+        <v>-462.4</v>
       </c>
       <c r="S89" t="n">
-        <v>90.90000000000001</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="90">
@@ -7499,34 +7499,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Def. de Belgrano</t>
+          <t>CA Mitre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Def. de Belgrano</t>
+          <t>CA Mitre</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Deportivo Moron</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J90" t="n">
         <v>0.91</v>
       </c>
       <c r="K90" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         </is>
       </c>
       <c r="M90" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
@@ -7542,19 +7542,19 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>0.0287</v>
+        <v>0.0573</v>
       </c>
       <c r="P90" t="n">
-        <v>2.87</v>
+        <v>5.73</v>
       </c>
       <c r="Q90" t="n">
-        <v>-3.528</v>
+        <v>-4.567</v>
       </c>
       <c r="R90" t="n">
-        <v>-352.8</v>
+        <v>-456.7</v>
       </c>
       <c r="S90" t="n">
-        <v>91</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="91">
@@ -7578,34 +7578,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CA Mitre</t>
+          <t>Def. de Belgrano</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>CA Mitre</t>
+          <t>Def. de Belgrano</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J91" t="n">
         <v>0.91</v>
       </c>
       <c r="K91" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         </is>
       </c>
       <c r="M91" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
@@ -7621,19 +7621,19 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>0.0573</v>
+        <v>0.0287</v>
       </c>
       <c r="P91" t="n">
-        <v>5.73</v>
+        <v>2.87</v>
       </c>
       <c r="Q91" t="n">
-        <v>-3.471</v>
+        <v>-4.538</v>
       </c>
       <c r="R91" t="n">
-        <v>-347.1</v>
+        <v>-453.8</v>
       </c>
       <c r="S91" t="n">
-        <v>91.09999999999999</v>
+        <v>90</v>
       </c>
     </row>
     <row r="92">
@@ -7706,13 +7706,13 @@
         <v>6.69</v>
       </c>
       <c r="Q92" t="n">
-        <v>-3.404</v>
+        <v>-4.471</v>
       </c>
       <c r="R92" t="n">
-        <v>-340.4</v>
+        <v>-447.1</v>
       </c>
       <c r="S92" t="n">
-        <v>91.2</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="93">
@@ -7785,13 +7785,13 @@
         <v>5.73</v>
       </c>
       <c r="Q93" t="n">
-        <v>-3.347</v>
+        <v>-4.414</v>
       </c>
       <c r="R93" t="n">
-        <v>-334.7</v>
+        <v>-441.4</v>
       </c>
       <c r="S93" t="n">
-        <v>91.3</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="94">
@@ -7864,13 +7864,13 @@
         <v>4.78</v>
       </c>
       <c r="Q94" t="n">
-        <v>-3.299</v>
+        <v>-4.366</v>
       </c>
       <c r="R94" t="n">
-        <v>-329.9</v>
+        <v>-436.6</v>
       </c>
       <c r="S94" t="n">
-        <v>91.40000000000001</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="95">
@@ -7943,13 +7943,13 @@
         <v>5.73</v>
       </c>
       <c r="Q95" t="n">
-        <v>-3.242</v>
+        <v>-4.309</v>
       </c>
       <c r="R95" t="n">
-        <v>-324.2</v>
+        <v>-430.9</v>
       </c>
       <c r="S95" t="n">
-        <v>91.5</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="96">
@@ -8022,13 +8022,13 @@
         <v>-100</v>
       </c>
       <c r="Q96" t="n">
-        <v>-4.242</v>
+        <v>-5.309</v>
       </c>
       <c r="R96" t="n">
-        <v>-424.2</v>
+        <v>-530.9</v>
       </c>
       <c r="S96" t="n">
-        <v>90.5</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="97">
@@ -8101,13 +8101,13 @@
         <v>3.82</v>
       </c>
       <c r="Q97" t="n">
-        <v>-4.204</v>
+        <v>-5.271</v>
       </c>
       <c r="R97" t="n">
-        <v>-420.4</v>
+        <v>-527.1</v>
       </c>
       <c r="S97" t="n">
-        <v>90.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="98">
@@ -8180,13 +8180,13 @@
         <v>8.6</v>
       </c>
       <c r="Q98" t="n">
-        <v>-4.118</v>
+        <v>-5.185</v>
       </c>
       <c r="R98" t="n">
-        <v>-411.8</v>
+        <v>-518.5</v>
       </c>
       <c r="S98" t="n">
-        <v>90.7</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="99">
@@ -8259,13 +8259,13 @@
         <v>12.41</v>
       </c>
       <c r="Q99" t="n">
-        <v>-3.993</v>
+        <v>-5.06</v>
       </c>
       <c r="R99" t="n">
-        <v>-399.3</v>
+        <v>-506</v>
       </c>
       <c r="S99" t="n">
-        <v>90.8</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="100">
@@ -8338,13 +8338,13 @@
         <v>11.46</v>
       </c>
       <c r="Q100" t="n">
-        <v>-3.879</v>
+        <v>-4.946</v>
       </c>
       <c r="R100" t="n">
-        <v>-387.9</v>
+        <v>-494.6</v>
       </c>
       <c r="S100" t="n">
-        <v>90.90000000000001</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="101">
@@ -8417,13 +8417,13 @@
         <v>7.64</v>
       </c>
       <c r="Q101" t="n">
-        <v>-3.802</v>
+        <v>-4.869</v>
       </c>
       <c r="R101" t="n">
-        <v>-380.2</v>
+        <v>-486.9</v>
       </c>
       <c r="S101" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="102">
@@ -8496,13 +8496,13 @@
         <v>1.91</v>
       </c>
       <c r="Q102" t="n">
-        <v>-3.783</v>
+        <v>-4.85</v>
       </c>
       <c r="R102" t="n">
-        <v>-378.3</v>
+        <v>-485</v>
       </c>
       <c r="S102" t="n">
-        <v>91.09999999999999</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="103">
@@ -8575,13 +8575,13 @@
         <v>9.550000000000001</v>
       </c>
       <c r="Q103" t="n">
-        <v>-3.688</v>
+        <v>-4.755</v>
       </c>
       <c r="R103" t="n">
-        <v>-368.8</v>
+        <v>-475.5</v>
       </c>
       <c r="S103" t="n">
-        <v>91.2</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="104">
@@ -8654,13 +8654,13 @@
         <v>4.78</v>
       </c>
       <c r="Q104" t="n">
-        <v>-3.64</v>
+        <v>-4.707</v>
       </c>
       <c r="R104" t="n">
-        <v>-364</v>
+        <v>-470.7</v>
       </c>
       <c r="S104" t="n">
-        <v>91.3</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="105">
@@ -8733,13 +8733,13 @@
         <v>6.69</v>
       </c>
       <c r="Q105" t="n">
-        <v>-3.573</v>
+        <v>-4.64</v>
       </c>
       <c r="R105" t="n">
-        <v>-357.3</v>
+        <v>-464</v>
       </c>
       <c r="S105" t="n">
-        <v>91.3</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="106">
@@ -8812,13 +8812,13 @@
         <v>5.73</v>
       </c>
       <c r="Q106" t="n">
-        <v>-3.516</v>
+        <v>-4.583</v>
       </c>
       <c r="R106" t="n">
-        <v>-351.6</v>
+        <v>-458.3</v>
       </c>
       <c r="S106" t="n">
-        <v>91.40000000000001</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="107">
@@ -8891,13 +8891,13 @@
         <v>5.73</v>
       </c>
       <c r="Q107" t="n">
-        <v>-3.459</v>
+        <v>-4.526</v>
       </c>
       <c r="R107" t="n">
-        <v>-345.9</v>
+        <v>-452.6</v>
       </c>
       <c r="S107" t="n">
-        <v>91.5</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="108">
@@ -8970,13 +8970,13 @@
         <v>-100</v>
       </c>
       <c r="Q108" t="n">
-        <v>-4.459</v>
+        <v>-5.526</v>
       </c>
       <c r="R108" t="n">
-        <v>-445.9</v>
+        <v>-552.6</v>
       </c>
       <c r="S108" t="n">
-        <v>90.7</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="109">
@@ -9049,13 +9049,13 @@
         <v>6.69</v>
       </c>
       <c r="Q109" t="n">
-        <v>-4.392</v>
+        <v>-5.459</v>
       </c>
       <c r="R109" t="n">
-        <v>-439.2</v>
+        <v>-545.9</v>
       </c>
       <c r="S109" t="n">
-        <v>90.7</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="110">
@@ -9128,13 +9128,13 @@
         <v>7.64</v>
       </c>
       <c r="Q110" t="n">
-        <v>-4.315</v>
+        <v>-5.382</v>
       </c>
       <c r="R110" t="n">
-        <v>-431.5</v>
+        <v>-538.2</v>
       </c>
       <c r="S110" t="n">
-        <v>90.8</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="111">
@@ -9207,13 +9207,13 @@
         <v>-100</v>
       </c>
       <c r="Q111" t="n">
-        <v>-5.315</v>
+        <v>-6.382</v>
       </c>
       <c r="R111" t="n">
-        <v>-531.5</v>
+        <v>-638.2</v>
       </c>
       <c r="S111" t="n">
-        <v>90</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="112">
@@ -9286,13 +9286,13 @@
         <v>7.64</v>
       </c>
       <c r="Q112" t="n">
-        <v>-5.239</v>
+        <v>-6.306</v>
       </c>
       <c r="R112" t="n">
-        <v>-523.9</v>
+        <v>-630.6</v>
       </c>
       <c r="S112" t="n">
-        <v>90.09999999999999</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="113">
@@ -9365,13 +9365,13 @@
         <v>5.73</v>
       </c>
       <c r="Q113" t="n">
-        <v>-5.182</v>
+        <v>-6.249</v>
       </c>
       <c r="R113" t="n">
-        <v>-518.2</v>
+        <v>-624.9</v>
       </c>
       <c r="S113" t="n">
-        <v>90.2</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="114">
@@ -9444,13 +9444,13 @@
         <v>2.87</v>
       </c>
       <c r="Q114" t="n">
-        <v>-5.153</v>
+        <v>-6.22</v>
       </c>
       <c r="R114" t="n">
-        <v>-515.3</v>
+        <v>-622</v>
       </c>
       <c r="S114" t="n">
-        <v>90.3</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="115">
@@ -9523,13 +9523,13 @@
         <v>-100</v>
       </c>
       <c r="Q115" t="n">
-        <v>-6.153</v>
+        <v>-7.22</v>
       </c>
       <c r="R115" t="n">
-        <v>-615.3</v>
+        <v>-722</v>
       </c>
       <c r="S115" t="n">
-        <v>89.5</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="116">
@@ -9602,13 +9602,13 @@
         <v>-100</v>
       </c>
       <c r="Q116" t="n">
-        <v>-7.153</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="R116" t="n">
-        <v>-715.3</v>
+        <v>-822</v>
       </c>
       <c r="S116" t="n">
-        <v>88.7</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="117">
@@ -9681,13 +9681,13 @@
         <v>4.78</v>
       </c>
       <c r="Q117" t="n">
-        <v>-7.105</v>
+        <v>-8.172000000000001</v>
       </c>
       <c r="R117" t="n">
-        <v>-710.5</v>
+        <v>-817.2</v>
       </c>
       <c r="S117" t="n">
-        <v>88.8</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="118">
@@ -9760,13 +9760,13 @@
         <v>2.87</v>
       </c>
       <c r="Q118" t="n">
-        <v>-7.076</v>
+        <v>-8.143000000000001</v>
       </c>
       <c r="R118" t="n">
-        <v>-707.6</v>
+        <v>-814.3</v>
       </c>
       <c r="S118" t="n">
-        <v>88.90000000000001</v>
+        <v>88</v>
       </c>
     </row>
     <row r="119">
@@ -9839,13 +9839,13 @@
         <v>4.78</v>
       </c>
       <c r="Q119" t="n">
-        <v>-7.029</v>
+        <v>-8.096</v>
       </c>
       <c r="R119" t="n">
-        <v>-702.9</v>
+        <v>-809.6</v>
       </c>
       <c r="S119" t="n">
-        <v>89</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="120">
@@ -9918,13 +9918,13 @@
         <v>3.82</v>
       </c>
       <c r="Q120" t="n">
-        <v>-6.99</v>
+        <v>-8.057</v>
       </c>
       <c r="R120" t="n">
-        <v>-699</v>
+        <v>-805.7</v>
       </c>
       <c r="S120" t="n">
-        <v>89.09999999999999</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="121">
@@ -9997,13 +9997,13 @@
         <v>3.82</v>
       </c>
       <c r="Q121" t="n">
-        <v>-6.952</v>
+        <v>-8.019</v>
       </c>
       <c r="R121" t="n">
-        <v>-695.2</v>
+        <v>-801.9</v>
       </c>
       <c r="S121" t="n">
-        <v>89.2</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="122">
@@ -10076,13 +10076,13 @@
         <v>5.73</v>
       </c>
       <c r="Q122" t="n">
-        <v>-6.895</v>
+        <v>-7.962</v>
       </c>
       <c r="R122" t="n">
-        <v>-689.5</v>
+        <v>-796.2</v>
       </c>
       <c r="S122" t="n">
-        <v>89.3</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="123">
@@ -10155,13 +10155,13 @@
         <v>4.78</v>
       </c>
       <c r="Q123" t="n">
-        <v>-6.847</v>
+        <v>-7.914</v>
       </c>
       <c r="R123" t="n">
-        <v>-684.7</v>
+        <v>-791.4</v>
       </c>
       <c r="S123" t="n">
-        <v>89.3</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="124">
@@ -10234,13 +10234,13 @@
         <v>5.73</v>
       </c>
       <c r="Q124" t="n">
-        <v>-6.79</v>
+        <v>-7.857</v>
       </c>
       <c r="R124" t="n">
-        <v>-679</v>
+        <v>-785.7</v>
       </c>
       <c r="S124" t="n">
-        <v>89.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="125">
@@ -10313,13 +10313,13 @@
         <v>-100</v>
       </c>
       <c r="Q125" t="n">
-        <v>-7.79</v>
+        <v>-8.856999999999999</v>
       </c>
       <c r="R125" t="n">
-        <v>-779</v>
+        <v>-885.7</v>
       </c>
       <c r="S125" t="n">
-        <v>88.7</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="126">
@@ -10392,13 +10392,13 @@
         <v>5.73</v>
       </c>
       <c r="Q126" t="n">
-        <v>-7.733</v>
+        <v>-8.798999999999999</v>
       </c>
       <c r="R126" t="n">
-        <v>-773.3</v>
+        <v>-879.9</v>
       </c>
       <c r="S126" t="n">
-        <v>88.8</v>
+        <v>88</v>
       </c>
     </row>
     <row r="127">
@@ -10471,13 +10471,13 @@
         <v>4.78</v>
       </c>
       <c r="Q127" t="n">
-        <v>-7.685</v>
+        <v>-8.752000000000001</v>
       </c>
       <c r="R127" t="n">
-        <v>-768.5</v>
+        <v>-875.2</v>
       </c>
       <c r="S127" t="n">
-        <v>88.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="128">
@@ -10501,22 +10501,22 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>WE SC</t>
+          <t>Dayrout</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>La Viena</t>
+          <t>Tersana</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>La Viena</t>
+          <t>Dayrout</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>WE SC</t>
+          <t>Tersana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -10528,7 +10528,7 @@
         <v>0.98</v>
       </c>
       <c r="K128" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="M128" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
@@ -10544,19 +10544,19 @@
         </is>
       </c>
       <c r="O128" t="n">
-        <v>0.0478</v>
+        <v>0.0382</v>
       </c>
       <c r="P128" t="n">
-        <v>4.78</v>
+        <v>3.82</v>
       </c>
       <c r="Q128" t="n">
-        <v>-7.637</v>
+        <v>-8.712999999999999</v>
       </c>
       <c r="R128" t="n">
-        <v>-763.7</v>
+        <v>-871.3</v>
       </c>
       <c r="S128" t="n">
-        <v>89</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="129">
@@ -10580,22 +10580,22 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dayrout</t>
+          <t>WE SC</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tersana</t>
+          <t>La Viena</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dayrout</t>
+          <t>La Viena</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Tersana</t>
+          <t>WE SC</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -10607,7 +10607,7 @@
         <v>0.98</v>
       </c>
       <c r="K129" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="M129" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N129" t="inlineStr">
         <is>
@@ -10623,19 +10623,19 @@
         </is>
       </c>
       <c r="O129" t="n">
-        <v>0.0382</v>
+        <v>0.0478</v>
       </c>
       <c r="P129" t="n">
-        <v>3.82</v>
+        <v>4.78</v>
       </c>
       <c r="Q129" t="n">
-        <v>-7.599</v>
+        <v>-8.666</v>
       </c>
       <c r="R129" t="n">
-        <v>-759.9</v>
+        <v>-866.6</v>
       </c>
       <c r="S129" t="n">
-        <v>89.09999999999999</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="130">
@@ -10708,13 +10708,13 @@
         <v>1.91</v>
       </c>
       <c r="Q130" t="n">
-        <v>-7.58</v>
+        <v>-8.647</v>
       </c>
       <c r="R130" t="n">
-        <v>-758</v>
+        <v>-864.7</v>
       </c>
       <c r="S130" t="n">
-        <v>89.09999999999999</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="131">
@@ -10787,13 +10787,13 @@
         <v>2.87</v>
       </c>
       <c r="Q131" t="n">
-        <v>-7.551</v>
+        <v>-8.618</v>
       </c>
       <c r="R131" t="n">
-        <v>-755.1</v>
+        <v>-861.8</v>
       </c>
       <c r="S131" t="n">
-        <v>89.2</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="132">
@@ -10866,13 +10866,13 @@
         <v>5.73</v>
       </c>
       <c r="Q132" t="n">
-        <v>-7.494</v>
+        <v>-8.561</v>
       </c>
       <c r="R132" t="n">
-        <v>-749.4</v>
+        <v>-856.1</v>
       </c>
       <c r="S132" t="n">
-        <v>89.3</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="133">
@@ -10945,13 +10945,13 @@
         <v>4.78</v>
       </c>
       <c r="Q133" t="n">
-        <v>-7.446</v>
+        <v>-8.513</v>
       </c>
       <c r="R133" t="n">
-        <v>-744.6</v>
+        <v>-851.3</v>
       </c>
       <c r="S133" t="n">
-        <v>89.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="134">
@@ -11024,13 +11024,13 @@
         <v>5.73</v>
       </c>
       <c r="Q134" t="n">
-        <v>-7.389</v>
+        <v>-8.455</v>
       </c>
       <c r="R134" t="n">
-        <v>-738.9</v>
+        <v>-845.5</v>
       </c>
       <c r="S134" t="n">
-        <v>89.5</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="135">
@@ -11103,13 +11103,13 @@
         <v>5.73</v>
       </c>
       <c r="Q135" t="n">
-        <v>-7.331</v>
+        <v>-8.398</v>
       </c>
       <c r="R135" t="n">
-        <v>-733.1</v>
+        <v>-839.8</v>
       </c>
       <c r="S135" t="n">
-        <v>89.59999999999999</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="136">
@@ -11182,13 +11182,13 @@
         <v>5.73</v>
       </c>
       <c r="Q136" t="n">
-        <v>-7.274</v>
+        <v>-8.340999999999999</v>
       </c>
       <c r="R136" t="n">
-        <v>-727.4</v>
+        <v>-834.1</v>
       </c>
       <c r="S136" t="n">
-        <v>89.59999999999999</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="137">
@@ -11261,13 +11261,13 @@
         <v>3.82</v>
       </c>
       <c r="Q137" t="n">
-        <v>-7.236</v>
+        <v>-8.303000000000001</v>
       </c>
       <c r="R137" t="n">
-        <v>-723.6</v>
+        <v>-830.3</v>
       </c>
       <c r="S137" t="n">
-        <v>89.7</v>
+        <v>89</v>
       </c>
     </row>
     <row r="138">
@@ -11340,13 +11340,13 @@
         <v>5.73</v>
       </c>
       <c r="Q138" t="n">
-        <v>-7.178</v>
+        <v>-8.244999999999999</v>
       </c>
       <c r="R138" t="n">
-        <v>-717.8</v>
+        <v>-824.5</v>
       </c>
       <c r="S138" t="n">
-        <v>89.8</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="139">
@@ -11419,13 +11419,13 @@
         <v>5.73</v>
       </c>
       <c r="Q139" t="n">
-        <v>-7.121</v>
+        <v>-8.188000000000001</v>
       </c>
       <c r="R139" t="n">
-        <v>-712.1</v>
+        <v>-818.8</v>
       </c>
       <c r="S139" t="n">
-        <v>89.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="140">
@@ -11498,13 +11498,13 @@
         <v>-100</v>
       </c>
       <c r="Q140" t="n">
-        <v>-8.121</v>
+        <v>-9.188000000000001</v>
       </c>
       <c r="R140" t="n">
-        <v>-812.1</v>
+        <v>-918.8</v>
       </c>
       <c r="S140" t="n">
-        <v>89.2</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="141">
@@ -11577,13 +11577,13 @@
         <v>4.78</v>
       </c>
       <c r="Q141" t="n">
-        <v>-8.073</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="R141" t="n">
-        <v>-807.3</v>
+        <v>-914</v>
       </c>
       <c r="S141" t="n">
-        <v>89.3</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="142">
@@ -11656,13 +11656,13 @@
         <v>5.73</v>
       </c>
       <c r="Q142" t="n">
-        <v>-8.016</v>
+        <v>-9.083</v>
       </c>
       <c r="R142" t="n">
-        <v>-801.6</v>
+        <v>-908.3</v>
       </c>
       <c r="S142" t="n">
-        <v>89.40000000000001</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="143">
@@ -11735,13 +11735,13 @@
         <v>2.87</v>
       </c>
       <c r="Q143" t="n">
-        <v>-7.987</v>
+        <v>-9.054</v>
       </c>
       <c r="R143" t="n">
-        <v>-798.7</v>
+        <v>-905.4</v>
       </c>
       <c r="S143" t="n">
-        <v>89.40000000000001</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="144">
@@ -11814,13 +11814,13 @@
         <v>2.87</v>
       </c>
       <c r="Q144" t="n">
-        <v>-7.959</v>
+        <v>-9.026</v>
       </c>
       <c r="R144" t="n">
-        <v>-795.9</v>
+        <v>-902.6</v>
       </c>
       <c r="S144" t="n">
-        <v>89.5</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="145">
@@ -11893,13 +11893,13 @@
         <v>2.87</v>
       </c>
       <c r="Q145" t="n">
-        <v>-7.93</v>
+        <v>-8.997</v>
       </c>
       <c r="R145" t="n">
-        <v>-793</v>
+        <v>-899.7</v>
       </c>
       <c r="S145" t="n">
-        <v>89.59999999999999</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="146">
@@ -11972,13 +11972,13 @@
         <v>3.82</v>
       </c>
       <c r="Q146" t="n">
-        <v>-7.892</v>
+        <v>-8.959</v>
       </c>
       <c r="R146" t="n">
-        <v>-789.2</v>
+        <v>-895.9</v>
       </c>
       <c r="S146" t="n">
-        <v>89.7</v>
+        <v>89</v>
       </c>
     </row>
     <row r="147">
@@ -12051,13 +12051,13 @@
         <v>-100</v>
       </c>
       <c r="Q147" t="n">
-        <v>-8.891999999999999</v>
+        <v>-9.959</v>
       </c>
       <c r="R147" t="n">
-        <v>-889.2</v>
+        <v>-995.9</v>
       </c>
       <c r="S147" t="n">
-        <v>89</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="148">
@@ -12130,13 +12130,13 @@
         <v>2.87</v>
       </c>
       <c r="Q148" t="n">
-        <v>-8.863</v>
+        <v>-9.93</v>
       </c>
       <c r="R148" t="n">
-        <v>-886.3</v>
+        <v>-993</v>
       </c>
       <c r="S148" t="n">
-        <v>89.09999999999999</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="149">
@@ -12209,13 +12209,13 @@
         <v>6.69</v>
       </c>
       <c r="Q149" t="n">
-        <v>-8.795999999999999</v>
+        <v>-9.863</v>
       </c>
       <c r="R149" t="n">
-        <v>-879.6</v>
+        <v>-986.3</v>
       </c>
       <c r="S149" t="n">
-        <v>89.2</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="150">
@@ -12288,13 +12288,13 @@
         <v>5.73</v>
       </c>
       <c r="Q150" t="n">
-        <v>-8.739000000000001</v>
+        <v>-9.805999999999999</v>
       </c>
       <c r="R150" t="n">
-        <v>-873.9</v>
+        <v>-980.6</v>
       </c>
       <c r="S150" t="n">
-        <v>89.3</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="151">
@@ -12367,13 +12367,13 @@
         <v>4.78</v>
       </c>
       <c r="Q151" t="n">
-        <v>-8.691000000000001</v>
+        <v>-9.757999999999999</v>
       </c>
       <c r="R151" t="n">
-        <v>-869.1</v>
+        <v>-975.8</v>
       </c>
       <c r="S151" t="n">
-        <v>89.3</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="152">
@@ -12446,13 +12446,13 @@
         <v>5.73</v>
       </c>
       <c r="Q152" t="n">
-        <v>-8.634</v>
+        <v>-9.701000000000001</v>
       </c>
       <c r="R152" t="n">
-        <v>-863.4</v>
+        <v>-970.1</v>
       </c>
       <c r="S152" t="n">
-        <v>89.40000000000001</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="153">
@@ -12525,13 +12525,13 @@
         <v>3.82</v>
       </c>
       <c r="Q153" t="n">
-        <v>-8.596</v>
+        <v>-9.662000000000001</v>
       </c>
       <c r="R153" t="n">
-        <v>-859.6</v>
+        <v>-966.2</v>
       </c>
       <c r="S153" t="n">
-        <v>89.5</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="154">
@@ -12604,13 +12604,13 @@
         <v>-100</v>
       </c>
       <c r="Q154" t="n">
-        <v>-9.596</v>
+        <v>-10.662</v>
       </c>
       <c r="R154" t="n">
-        <v>-959.6</v>
+        <v>-1066.2</v>
       </c>
       <c r="S154" t="n">
-        <v>88.90000000000001</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="155">
@@ -12683,13 +12683,13 @@
         <v>3.82</v>
       </c>
       <c r="Q155" t="n">
-        <v>-9.557</v>
+        <v>-10.624</v>
       </c>
       <c r="R155" t="n">
-        <v>-955.7</v>
+        <v>-1062.4</v>
       </c>
       <c r="S155" t="n">
-        <v>89</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="156">
@@ -12762,13 +12762,13 @@
         <v>5.73</v>
       </c>
       <c r="Q156" t="n">
-        <v>-9.5</v>
+        <v>-10.567</v>
       </c>
       <c r="R156" t="n">
-        <v>-950</v>
+        <v>-1056.7</v>
       </c>
       <c r="S156" t="n">
-        <v>89</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="157">
@@ -12841,13 +12841,13 @@
         <v>4.78</v>
       </c>
       <c r="Q157" t="n">
-        <v>-9.452</v>
+        <v>-10.519</v>
       </c>
       <c r="R157" t="n">
-        <v>-945.2</v>
+        <v>-1051.9</v>
       </c>
       <c r="S157" t="n">
-        <v>89.09999999999999</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="158">
@@ -12920,13 +12920,13 @@
         <v>3.82</v>
       </c>
       <c r="Q158" t="n">
-        <v>-9.414</v>
+        <v>-10.481</v>
       </c>
       <c r="R158" t="n">
-        <v>-941.4</v>
+        <v>-1048.1</v>
       </c>
       <c r="S158" t="n">
-        <v>89.2</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="159">
@@ -12999,13 +12999,13 @@
         <v>5.73</v>
       </c>
       <c r="Q159" t="n">
-        <v>-9.356999999999999</v>
+        <v>-10.424</v>
       </c>
       <c r="R159" t="n">
-        <v>-935.7</v>
+        <v>-1042.4</v>
       </c>
       <c r="S159" t="n">
-        <v>89.2</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="160">
@@ -13078,13 +13078,13 @@
         <v>2.87</v>
       </c>
       <c r="Q160" t="n">
-        <v>-9.327999999999999</v>
+        <v>-10.395</v>
       </c>
       <c r="R160" t="n">
-        <v>-932.8</v>
+        <v>-1039.5</v>
       </c>
       <c r="S160" t="n">
-        <v>89.3</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="161">
@@ -13157,13 +13157,13 @@
         <v>4.78</v>
       </c>
       <c r="Q161" t="n">
-        <v>-9.279999999999999</v>
+        <v>-10.347</v>
       </c>
       <c r="R161" t="n">
-        <v>-928</v>
+        <v>-1034.7</v>
       </c>
       <c r="S161" t="n">
-        <v>89.40000000000001</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="162">
@@ -13236,13 +13236,13 @@
         <v>5.73</v>
       </c>
       <c r="Q162" t="n">
-        <v>-9.223000000000001</v>
+        <v>-10.29</v>
       </c>
       <c r="R162" t="n">
-        <v>-922.3</v>
+        <v>-1029</v>
       </c>
       <c r="S162" t="n">
-        <v>89.40000000000001</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="163">
@@ -13315,13 +13315,13 @@
         <v>5.73</v>
       </c>
       <c r="Q163" t="n">
-        <v>-9.166</v>
+        <v>-10.233</v>
       </c>
       <c r="R163" t="n">
-        <v>-916.6</v>
+        <v>-1023.3</v>
       </c>
       <c r="S163" t="n">
-        <v>89.5</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="164">
@@ -13394,13 +13394,13 @@
         <v>5.73</v>
       </c>
       <c r="Q164" t="n">
-        <v>-9.108000000000001</v>
+        <v>-10.175</v>
       </c>
       <c r="R164" t="n">
-        <v>-910.8</v>
+        <v>-1017.5</v>
       </c>
       <c r="S164" t="n">
-        <v>89.59999999999999</v>
+        <v>89</v>
       </c>
     </row>
     <row r="165">
@@ -13473,13 +13473,13 @@
         <v>4.78</v>
       </c>
       <c r="Q165" t="n">
-        <v>-9.061</v>
+        <v>-10.127</v>
       </c>
       <c r="R165" t="n">
-        <v>-906.1</v>
+        <v>-1012.7</v>
       </c>
       <c r="S165" t="n">
-        <v>89.59999999999999</v>
+        <v>89</v>
       </c>
     </row>
     <row r="166">
@@ -13552,13 +13552,13 @@
         <v>8.6</v>
       </c>
       <c r="Q166" t="n">
-        <v>-8.975</v>
+        <v>-10.041</v>
       </c>
       <c r="R166" t="n">
-        <v>-897.5</v>
+        <v>-1004.1</v>
       </c>
       <c r="S166" t="n">
-        <v>89.7</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="167">
@@ -13631,13 +13631,13 @@
         <v>9.550000000000001</v>
       </c>
       <c r="Q167" t="n">
-        <v>-8.879</v>
+        <v>-9.946</v>
       </c>
       <c r="R167" t="n">
-        <v>-887.9</v>
+        <v>-994.6</v>
       </c>
       <c r="S167" t="n">
-        <v>89.8</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="168">
@@ -13710,13 +13710,13 @@
         <v>8.6</v>
       </c>
       <c r="Q168" t="n">
-        <v>-8.792999999999999</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="R168" t="n">
-        <v>-879.3</v>
+        <v>-986</v>
       </c>
       <c r="S168" t="n">
-        <v>89.8</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="169">
@@ -13789,13 +13789,13 @@
         <v>4.78</v>
       </c>
       <c r="Q169" t="n">
-        <v>-8.744999999999999</v>
+        <v>-9.811999999999999</v>
       </c>
       <c r="R169" t="n">
-        <v>-874.5</v>
+        <v>-981.2</v>
       </c>
       <c r="S169" t="n">
-        <v>89.90000000000001</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="170">
@@ -13819,34 +13819,34 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>La Viena</t>
+          <t>Aswan SC</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tersana</t>
+          <t>Tanta</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Tersana</t>
+          <t>Tanta</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>La Viena</t>
+          <t>Aswan SC</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="J170" t="n">
         <v>0.98</v>
       </c>
       <c r="K170" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         </is>
       </c>
       <c r="M170" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N170" t="inlineStr">
         <is>
@@ -13862,19 +13862,19 @@
         </is>
       </c>
       <c r="O170" t="n">
-        <v>0.0382</v>
+        <v>0.0573</v>
       </c>
       <c r="P170" t="n">
-        <v>3.82</v>
+        <v>5.73</v>
       </c>
       <c r="Q170" t="n">
-        <v>-8.707000000000001</v>
+        <v>-9.755000000000001</v>
       </c>
       <c r="R170" t="n">
-        <v>-870.7</v>
+        <v>-975.5</v>
       </c>
       <c r="S170" t="n">
-        <v>89.90000000000001</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="171">
@@ -13898,34 +13898,34 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Aswan SC</t>
+          <t>La Viena</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tanta</t>
+          <t>Tersana</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Tanta</t>
+          <t>Tersana</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Aswan SC</t>
+          <t>La Viena</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J171" t="n">
         <v>0.98</v>
       </c>
       <c r="K171" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         </is>
       </c>
       <c r="M171" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N171" t="inlineStr">
         <is>
@@ -13941,19 +13941,19 @@
         </is>
       </c>
       <c r="O171" t="n">
-        <v>0.0573</v>
+        <v>0.0382</v>
       </c>
       <c r="P171" t="n">
-        <v>5.73</v>
+        <v>3.82</v>
       </c>
       <c r="Q171" t="n">
-        <v>-8.65</v>
+        <v>-9.717000000000001</v>
       </c>
       <c r="R171" t="n">
-        <v>-865</v>
+        <v>-971.7</v>
       </c>
       <c r="S171" t="n">
-        <v>90</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="172">
@@ -14026,13 +14026,13 @@
         <v>7.64</v>
       </c>
       <c r="Q172" t="n">
-        <v>-8.573</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="R172" t="n">
-        <v>-857.3</v>
+        <v>-964</v>
       </c>
       <c r="S172" t="n">
-        <v>90.09999999999999</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="173">
@@ -14105,13 +14105,13 @@
         <v>2.87</v>
       </c>
       <c r="Q173" t="n">
-        <v>-8.545</v>
+        <v>-9.612</v>
       </c>
       <c r="R173" t="n">
-        <v>-854.5</v>
+        <v>-961.2</v>
       </c>
       <c r="S173" t="n">
-        <v>90.09999999999999</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="174">
@@ -14184,13 +14184,13 @@
         <v>4.78</v>
       </c>
       <c r="Q174" t="n">
-        <v>-8.497</v>
+        <v>-9.564</v>
       </c>
       <c r="R174" t="n">
-        <v>-849.7</v>
+        <v>-956.4</v>
       </c>
       <c r="S174" t="n">
-        <v>90.2</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="175">
@@ -14263,13 +14263,13 @@
         <v>5.73</v>
       </c>
       <c r="Q175" t="n">
-        <v>-8.44</v>
+        <v>-9.506</v>
       </c>
       <c r="R175" t="n">
-        <v>-844</v>
+        <v>-950.6</v>
       </c>
       <c r="S175" t="n">
-        <v>90.2</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="176">
@@ -14342,13 +14342,13 @@
         <v>12.41</v>
       </c>
       <c r="Q176" t="n">
-        <v>-8.315</v>
+        <v>-9.382</v>
       </c>
       <c r="R176" t="n">
-        <v>-831.5</v>
+        <v>-938.2</v>
       </c>
       <c r="S176" t="n">
-        <v>90.3</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="177">
@@ -14421,13 +14421,13 @@
         <v>4.78</v>
       </c>
       <c r="Q177" t="n">
-        <v>-8.268000000000001</v>
+        <v>-9.334</v>
       </c>
       <c r="R177" t="n">
-        <v>-826.8</v>
+        <v>-933.4</v>
       </c>
       <c r="S177" t="n">
-        <v>90.3</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="178">
@@ -14500,13 +14500,13 @@
         <v>4.78</v>
       </c>
       <c r="Q178" t="n">
-        <v>-8.220000000000001</v>
+        <v>-9.287000000000001</v>
       </c>
       <c r="R178" t="n">
-        <v>-822</v>
+        <v>-928.7</v>
       </c>
       <c r="S178" t="n">
-        <v>90.40000000000001</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="179">
@@ -14579,13 +14579,13 @@
         <v>5.73</v>
       </c>
       <c r="Q179" t="n">
-        <v>-8.163</v>
+        <v>-9.228999999999999</v>
       </c>
       <c r="R179" t="n">
-        <v>-816.3</v>
+        <v>-922.9</v>
       </c>
       <c r="S179" t="n">
-        <v>90.40000000000001</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="180">
@@ -14658,13 +14658,13 @@
         <v>5.73</v>
       </c>
       <c r="Q180" t="n">
-        <v>-8.105</v>
+        <v>-9.172000000000001</v>
       </c>
       <c r="R180" t="n">
-        <v>-810.5</v>
+        <v>-917.2</v>
       </c>
       <c r="S180" t="n">
-        <v>90.5</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="181">
@@ -14737,13 +14737,13 @@
         <v>10.51</v>
       </c>
       <c r="Q181" t="n">
-        <v>-8</v>
+        <v>-9.067</v>
       </c>
       <c r="R181" t="n">
-        <v>-800</v>
+        <v>-906.7</v>
       </c>
       <c r="S181" t="n">
-        <v>90.59999999999999</v>
+        <v>90</v>
       </c>
     </row>
     <row r="182">
@@ -14816,13 +14816,13 @@
         <v>6.69</v>
       </c>
       <c r="Q182" t="n">
-        <v>-7.933</v>
+        <v>-9</v>
       </c>
       <c r="R182" t="n">
-        <v>-793.3</v>
+        <v>-900</v>
       </c>
       <c r="S182" t="n">
-        <v>90.59999999999999</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="183">
@@ -14895,13 +14895,13 @@
         <v>4.78</v>
       </c>
       <c r="Q183" t="n">
-        <v>-7.885</v>
+        <v>-8.952</v>
       </c>
       <c r="R183" t="n">
-        <v>-788.5</v>
+        <v>-895.2</v>
       </c>
       <c r="S183" t="n">
-        <v>90.7</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="184">
@@ -14974,13 +14974,13 @@
         <v>6.69</v>
       </c>
       <c r="Q184" t="n">
-        <v>-7.819</v>
+        <v>-8.885</v>
       </c>
       <c r="R184" t="n">
-        <v>-781.9</v>
+        <v>-888.5</v>
       </c>
       <c r="S184" t="n">
-        <v>90.7</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="185">
@@ -15053,13 +15053,13 @@
         <v>4.78</v>
       </c>
       <c r="Q185" t="n">
-        <v>-7.771</v>
+        <v>-8.837999999999999</v>
       </c>
       <c r="R185" t="n">
-        <v>-777.1</v>
+        <v>-883.8</v>
       </c>
       <c r="S185" t="n">
-        <v>90.8</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="186">
@@ -15132,13 +15132,13 @@
         <v>3.82</v>
       </c>
       <c r="Q186" t="n">
-        <v>-7.733</v>
+        <v>-8.798999999999999</v>
       </c>
       <c r="R186" t="n">
-        <v>-773.3</v>
+        <v>-879.9</v>
       </c>
       <c r="S186" t="n">
-        <v>90.8</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="187">
@@ -15211,13 +15211,13 @@
         <v>2.87</v>
       </c>
       <c r="Q187" t="n">
-        <v>-7.704</v>
+        <v>-8.771000000000001</v>
       </c>
       <c r="R187" t="n">
-        <v>-770.4</v>
+        <v>-877.1</v>
       </c>
       <c r="S187" t="n">
-        <v>90.90000000000001</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="188">
@@ -15290,13 +15290,13 @@
         <v>3.82</v>
       </c>
       <c r="Q188" t="n">
-        <v>-7.666</v>
+        <v>-8.731999999999999</v>
       </c>
       <c r="R188" t="n">
-        <v>-766.6</v>
+        <v>-873.2</v>
       </c>
       <c r="S188" t="n">
-        <v>90.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="189">
@@ -15369,13 +15369,13 @@
         <v>4.78</v>
       </c>
       <c r="Q189" t="n">
-        <v>-7.618</v>
+        <v>-8.685</v>
       </c>
       <c r="R189" t="n">
-        <v>-761.8</v>
+        <v>-868.5</v>
       </c>
       <c r="S189" t="n">
-        <v>91</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="190">
@@ -15448,13 +15448,13 @@
         <v>-100</v>
       </c>
       <c r="Q190" t="n">
-        <v>-8.618</v>
+        <v>-9.685</v>
       </c>
       <c r="R190" t="n">
-        <v>-861.8</v>
+        <v>-968.5</v>
       </c>
       <c r="S190" t="n">
-        <v>90.5</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="191">
@@ -15527,13 +15527,13 @@
         <v>-100</v>
       </c>
       <c r="Q191" t="n">
-        <v>-9.618</v>
+        <v>-10.685</v>
       </c>
       <c r="R191" t="n">
-        <v>-961.8</v>
+        <v>-1068.5</v>
       </c>
       <c r="S191" t="n">
-        <v>90</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="192">
@@ -15606,13 +15606,13 @@
         <v>5.73</v>
       </c>
       <c r="Q192" t="n">
-        <v>-9.561</v>
+        <v>-10.627</v>
       </c>
       <c r="R192" t="n">
-        <v>-956.1</v>
+        <v>-1062.7</v>
       </c>
       <c r="S192" t="n">
-        <v>90.09999999999999</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="193">
@@ -15685,13 +15685,13 @@
         <v>10.51</v>
       </c>
       <c r="Q193" t="n">
-        <v>-9.455</v>
+        <v>-10.522</v>
       </c>
       <c r="R193" t="n">
-        <v>-945.5</v>
+        <v>-1052.2</v>
       </c>
       <c r="S193" t="n">
-        <v>90.09999999999999</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="194">
@@ -15764,13 +15764,13 @@
         <v>4.78</v>
       </c>
       <c r="Q194" t="n">
-        <v>-9.407999999999999</v>
+        <v>-10.474</v>
       </c>
       <c r="R194" t="n">
-        <v>-940.8</v>
+        <v>-1047.4</v>
       </c>
       <c r="S194" t="n">
-        <v>90.2</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="195">
@@ -15843,13 +15843,13 @@
         <v>-100</v>
       </c>
       <c r="Q195" t="n">
-        <v>-10.408</v>
+        <v>-11.474</v>
       </c>
       <c r="R195" t="n">
-        <v>-1040.8</v>
+        <v>-1147.4</v>
       </c>
       <c r="S195" t="n">
-        <v>89.7</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="196">
@@ -15922,13 +15922,13 @@
         <v>2.87</v>
       </c>
       <c r="Q196" t="n">
-        <v>-10.379</v>
+        <v>-11.446</v>
       </c>
       <c r="R196" t="n">
-        <v>-1037.9</v>
+        <v>-1144.6</v>
       </c>
       <c r="S196" t="n">
-        <v>89.7</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="197">
@@ -16001,13 +16001,13 @@
         <v>2.87</v>
       </c>
       <c r="Q197" t="n">
-        <v>-10.35</v>
+        <v>-11.417</v>
       </c>
       <c r="R197" t="n">
-        <v>-1035</v>
+        <v>-1141.7</v>
       </c>
       <c r="S197" t="n">
-        <v>89.8</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="198">
@@ -16080,13 +16080,13 @@
         <v>0.96</v>
       </c>
       <c r="Q198" t="n">
-        <v>-10.341</v>
+        <v>-11.407</v>
       </c>
       <c r="R198" t="n">
-        <v>-1034.1</v>
+        <v>-1140.7</v>
       </c>
       <c r="S198" t="n">
-        <v>89.8</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="199">
@@ -16159,13 +16159,13 @@
         <v>6.69</v>
       </c>
       <c r="Q199" t="n">
-        <v>-10.274</v>
+        <v>-11.341</v>
       </c>
       <c r="R199" t="n">
-        <v>-1027.4</v>
+        <v>-1134.1</v>
       </c>
       <c r="S199" t="n">
-        <v>89.90000000000001</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="200">
@@ -16238,13 +16238,13 @@
         <v>8.6</v>
       </c>
       <c r="Q200" t="n">
-        <v>-10.188</v>
+        <v>-11.255</v>
       </c>
       <c r="R200" t="n">
-        <v>-1018.8</v>
+        <v>-1125.5</v>
       </c>
       <c r="S200" t="n">
-        <v>89.90000000000001</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="201">
@@ -16317,13 +16317,13 @@
         <v>5.73</v>
       </c>
       <c r="Q201" t="n">
-        <v>-10.13</v>
+        <v>-11.197</v>
       </c>
       <c r="R201" t="n">
-        <v>-1013</v>
+        <v>-1119.7</v>
       </c>
       <c r="S201" t="n">
-        <v>90</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="202">
@@ -16396,13 +16396,13 @@
         <v>6.69</v>
       </c>
       <c r="Q202" t="n">
-        <v>-10.064</v>
+        <v>-11.13</v>
       </c>
       <c r="R202" t="n">
-        <v>-1006.4</v>
+        <v>-1113</v>
       </c>
       <c r="S202" t="n">
-        <v>90</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="203">
@@ -16475,13 +16475,13 @@
         <v>4.78</v>
       </c>
       <c r="Q203" t="n">
-        <v>-10.016</v>
+        <v>-11.083</v>
       </c>
       <c r="R203" t="n">
-        <v>-1001.6</v>
+        <v>-1108.3</v>
       </c>
       <c r="S203" t="n">
-        <v>90.09999999999999</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="204">
@@ -16554,13 +16554,13 @@
         <v>5.73</v>
       </c>
       <c r="Q204" t="n">
-        <v>-9.958</v>
+        <v>-11.025</v>
       </c>
       <c r="R204" t="n">
-        <v>-995.8</v>
+        <v>-1102.5</v>
       </c>
       <c r="S204" t="n">
-        <v>90.09999999999999</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="205">
@@ -16633,13 +16633,13 @@
         <v>3.82</v>
       </c>
       <c r="Q205" t="n">
-        <v>-9.92</v>
+        <v>-10.987</v>
       </c>
       <c r="R205" t="n">
-        <v>-992</v>
+        <v>-1098.7</v>
       </c>
       <c r="S205" t="n">
-        <v>90.2</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="206">
@@ -16712,13 +16712,13 @@
         <v>3.82</v>
       </c>
       <c r="Q206" t="n">
-        <v>-9.882</v>
+        <v>-10.949</v>
       </c>
       <c r="R206" t="n">
-        <v>-988.2</v>
+        <v>-1094.9</v>
       </c>
       <c r="S206" t="n">
-        <v>90.2</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="207">
@@ -16791,13 +16791,13 @@
         <v>6.69</v>
       </c>
       <c r="Q207" t="n">
-        <v>-9.815</v>
+        <v>-10.882</v>
       </c>
       <c r="R207" t="n">
-        <v>-981.5</v>
+        <v>-1088.2</v>
       </c>
       <c r="S207" t="n">
-        <v>90.3</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="208">
@@ -16870,13 +16870,13 @@
         <v>4.78</v>
       </c>
       <c r="Q208" t="n">
-        <v>-9.766999999999999</v>
+        <v>-10.834</v>
       </c>
       <c r="R208" t="n">
-        <v>-976.7</v>
+        <v>-1083.4</v>
       </c>
       <c r="S208" t="n">
-        <v>90.3</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="209">
@@ -16900,34 +16900,34 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Kahrabaa Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>El Ismaily</t>
+          <t>ZED</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Kahrabaa Ismailia</t>
+          <t>ZED</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>El Ismaily</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J209" t="n">
         <v>1.05</v>
       </c>
       <c r="K209" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
@@ -16935,7 +16935,7 @@
         </is>
       </c>
       <c r="M209" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N209" t="inlineStr">
         <is>
@@ -16943,19 +16943,19 @@
         </is>
       </c>
       <c r="O209" t="n">
-        <v>0.0573</v>
+        <v>0.0669</v>
       </c>
       <c r="P209" t="n">
-        <v>5.73</v>
+        <v>6.69</v>
       </c>
       <c r="Q209" t="n">
-        <v>-9.710000000000001</v>
+        <v>-10.767</v>
       </c>
       <c r="R209" t="n">
-        <v>-971</v>
+        <v>-1076.7</v>
       </c>
       <c r="S209" t="n">
-        <v>90.40000000000001</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="210">
@@ -17028,13 +17028,13 @@
         <v>-100</v>
       </c>
       <c r="Q210" t="n">
-        <v>-10.71</v>
+        <v>-11.767</v>
       </c>
       <c r="R210" t="n">
-        <v>-1071</v>
+        <v>-1176.7</v>
       </c>
       <c r="S210" t="n">
-        <v>90</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="211">
@@ -17107,13 +17107,13 @@
         <v>8.6</v>
       </c>
       <c r="Q211" t="n">
-        <v>-10.624</v>
+        <v>-11.681</v>
       </c>
       <c r="R211" t="n">
-        <v>-1062.4</v>
+        <v>-1168.1</v>
       </c>
       <c r="S211" t="n">
-        <v>90</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="212">
@@ -17186,13 +17186,13 @@
         <v>4.78</v>
       </c>
       <c r="Q212" t="n">
-        <v>-10.576</v>
+        <v>-11.633</v>
       </c>
       <c r="R212" t="n">
-        <v>-1057.6</v>
+        <v>-1163.3</v>
       </c>
       <c r="S212" t="n">
-        <v>90</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="213">
@@ -17265,13 +17265,13 @@
         <v>2.87</v>
       </c>
       <c r="Q213" t="n">
-        <v>-10.548</v>
+        <v>-11.605</v>
       </c>
       <c r="R213" t="n">
-        <v>-1054.8</v>
+        <v>-1160.5</v>
       </c>
       <c r="S213" t="n">
-        <v>90.09999999999999</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="214">
@@ -17344,13 +17344,13 @@
         <v>3.82</v>
       </c>
       <c r="Q214" t="n">
-        <v>-10.509</v>
+        <v>-11.567</v>
       </c>
       <c r="R214" t="n">
-        <v>-1050.9</v>
+        <v>-1156.7</v>
       </c>
       <c r="S214" t="n">
-        <v>90.09999999999999</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="215">
@@ -17423,13 +17423,13 @@
         <v>4.78</v>
       </c>
       <c r="Q215" t="n">
-        <v>-10.462</v>
+        <v>-11.519</v>
       </c>
       <c r="R215" t="n">
-        <v>-1046.2</v>
+        <v>-1151.9</v>
       </c>
       <c r="S215" t="n">
-        <v>90.2</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="216">
@@ -17502,13 +17502,13 @@
         <v>7.64</v>
       </c>
       <c r="Q216" t="n">
-        <v>-10.385</v>
+        <v>-11.442</v>
       </c>
       <c r="R216" t="n">
-        <v>-1038.5</v>
+        <v>-1144.2</v>
       </c>
       <c r="S216" t="n">
-        <v>90.2</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="217">
@@ -17581,13 +17581,13 @@
         <v>3.82</v>
       </c>
       <c r="Q217" t="n">
-        <v>-10.347</v>
+        <v>-11.404</v>
       </c>
       <c r="R217" t="n">
-        <v>-1034.7</v>
+        <v>-1140.4</v>
       </c>
       <c r="S217" t="n">
-        <v>90.3</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="218">
@@ -17660,13 +17660,13 @@
         <v>4.78</v>
       </c>
       <c r="Q218" t="n">
-        <v>-10.299</v>
+        <v>-11.356</v>
       </c>
       <c r="R218" t="n">
-        <v>-1029.9</v>
+        <v>-1135.6</v>
       </c>
       <c r="S218" t="n">
-        <v>90.3</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="219">
@@ -17739,13 +17739,13 @@
         <v>3.82</v>
       </c>
       <c r="Q219" t="n">
-        <v>-10.261</v>
+        <v>-11.318</v>
       </c>
       <c r="R219" t="n">
-        <v>-1026.1</v>
+        <v>-1131.8</v>
       </c>
       <c r="S219" t="n">
-        <v>90.40000000000001</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="220">
@@ -17818,13 +17818,13 @@
         <v>4.78</v>
       </c>
       <c r="Q220" t="n">
-        <v>-10.213</v>
+        <v>-11.27</v>
       </c>
       <c r="R220" t="n">
-        <v>-1021.3</v>
+        <v>-1127</v>
       </c>
       <c r="S220" t="n">
-        <v>90.40000000000001</v>
+        <v>90</v>
       </c>
     </row>
     <row r="221">
@@ -17897,13 +17897,13 @@
         <v>6.69</v>
       </c>
       <c r="Q221" t="n">
-        <v>-10.146</v>
+        <v>-11.203</v>
       </c>
       <c r="R221" t="n">
-        <v>-1014.6</v>
+        <v>-1120.3</v>
       </c>
       <c r="S221" t="n">
-        <v>90.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="222">
@@ -17976,13 +17976,13 @@
         <v>6.69</v>
       </c>
       <c r="Q222" t="n">
-        <v>-10.079</v>
+        <v>-11.137</v>
       </c>
       <c r="R222" t="n">
-        <v>-1007.9</v>
+        <v>-1113.7</v>
       </c>
       <c r="S222" t="n">
-        <v>90.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="223">
@@ -18055,13 +18055,13 @@
         <v>5.73</v>
       </c>
       <c r="Q223" t="n">
-        <v>-10.022</v>
+        <v>-11.079</v>
       </c>
       <c r="R223" t="n">
-        <v>-1002.2</v>
+        <v>-1107.9</v>
       </c>
       <c r="S223" t="n">
-        <v>90.5</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="224">
@@ -18134,13 +18134,13 @@
         <v>5.73</v>
       </c>
       <c r="Q224" t="n">
-        <v>-9.965</v>
+        <v>-11.022</v>
       </c>
       <c r="R224" t="n">
-        <v>-996.5</v>
+        <v>-1102.2</v>
       </c>
       <c r="S224" t="n">
-        <v>90.59999999999999</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="225">
@@ -18213,13 +18213,13 @@
         <v>2.87</v>
       </c>
       <c r="Q225" t="n">
-        <v>-9.936</v>
+        <v>-10.993</v>
       </c>
       <c r="R225" t="n">
-        <v>-993.6</v>
+        <v>-1099.3</v>
       </c>
       <c r="S225" t="n">
-        <v>90.59999999999999</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="226">
@@ -18292,13 +18292,13 @@
         <v>2.87</v>
       </c>
       <c r="Q226" t="n">
-        <v>-9.907</v>
+        <v>-10.965</v>
       </c>
       <c r="R226" t="n">
-        <v>-990.7</v>
+        <v>-1096.5</v>
       </c>
       <c r="S226" t="n">
-        <v>90.7</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="227">
@@ -18371,13 +18371,13 @@
         <v>4.78</v>
       </c>
       <c r="Q227" t="n">
-        <v>-9.859</v>
+        <v>-10.917</v>
       </c>
       <c r="R227" t="n">
-        <v>-985.9</v>
+        <v>-1091.7</v>
       </c>
       <c r="S227" t="n">
-        <v>90.7</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="228">
@@ -18450,13 +18450,13 @@
         <v>4.78</v>
       </c>
       <c r="Q228" t="n">
-        <v>-9.811999999999999</v>
+        <v>-10.869</v>
       </c>
       <c r="R228" t="n">
-        <v>-981.2</v>
+        <v>-1086.9</v>
       </c>
       <c r="S228" t="n">
-        <v>90.7</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="229">
@@ -18529,13 +18529,13 @@
         <v>5.73</v>
       </c>
       <c r="Q229" t="n">
-        <v>-9.754</v>
+        <v>-10.812</v>
       </c>
       <c r="R229" t="n">
-        <v>-975.4</v>
+        <v>-1081.2</v>
       </c>
       <c r="S229" t="n">
-        <v>90.8</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="230">
@@ -18559,34 +18559,34 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="J230" t="n">
         <v>1</v>
       </c>
       <c r="K230" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="L230" t="inlineStr">
         <is>
@@ -18594,27 +18594,27 @@
         </is>
       </c>
       <c r="M230" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="O230" t="n">
-        <v>0.0382</v>
+        <v>-1</v>
       </c>
       <c r="P230" t="n">
-        <v>3.82</v>
+        <v>-100</v>
       </c>
       <c r="Q230" t="n">
-        <v>-9.715999999999999</v>
+        <v>-11.812</v>
       </c>
       <c r="R230" t="n">
-        <v>-971.6</v>
+        <v>-1181.2</v>
       </c>
       <c r="S230" t="n">
-        <v>90.8</v>
+        <v>90</v>
       </c>
     </row>
     <row r="231">
@@ -18638,34 +18638,34 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J231" t="n">
         <v>1</v>
       </c>
       <c r="K231" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
@@ -18677,23 +18677,23 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="O231" t="n">
-        <v>-1</v>
+        <v>0.0478</v>
       </c>
       <c r="P231" t="n">
-        <v>-100</v>
+        <v>4.78</v>
       </c>
       <c r="Q231" t="n">
-        <v>-10.716</v>
+        <v>-11.764</v>
       </c>
       <c r="R231" t="n">
-        <v>-1071.6</v>
+        <v>-1176.4</v>
       </c>
       <c r="S231" t="n">
-        <v>90.40000000000001</v>
+        <v>90</v>
       </c>
     </row>
     <row r="232">
@@ -18766,13 +18766,13 @@
         <v>7.64</v>
       </c>
       <c r="Q232" t="n">
-        <v>-10.64</v>
+        <v>-11.687</v>
       </c>
       <c r="R232" t="n">
-        <v>-1064</v>
+        <v>-1168.7</v>
       </c>
       <c r="S232" t="n">
-        <v>90.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="233">
@@ -18845,13 +18845,13 @@
         <v>3.82</v>
       </c>
       <c r="Q233" t="n">
-        <v>-10.602</v>
+        <v>-11.649</v>
       </c>
       <c r="R233" t="n">
-        <v>-1060.2</v>
+        <v>-1164.9</v>
       </c>
       <c r="S233" t="n">
-        <v>90.5</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="234">
@@ -18924,13 +18924,13 @@
         <v>8.6</v>
       </c>
       <c r="Q234" t="n">
-        <v>-10.516</v>
+        <v>-11.563</v>
       </c>
       <c r="R234" t="n">
-        <v>-1051.6</v>
+        <v>-1156.3</v>
       </c>
       <c r="S234" t="n">
-        <v>90.59999999999999</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="235">
@@ -19003,13 +19003,13 @@
         <v>6.69</v>
       </c>
       <c r="Q235" t="n">
-        <v>-10.449</v>
+        <v>-11.496</v>
       </c>
       <c r="R235" t="n">
-        <v>-1044.9</v>
+        <v>-1149.6</v>
       </c>
       <c r="S235" t="n">
-        <v>90.59999999999999</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="236">
@@ -19082,13 +19082,13 @@
         <v>1.91</v>
       </c>
       <c r="Q236" t="n">
-        <v>-10.43</v>
+        <v>-11.477</v>
       </c>
       <c r="R236" t="n">
-        <v>-1043</v>
+        <v>-1147.7</v>
       </c>
       <c r="S236" t="n">
-        <v>90.59999999999999</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="237">
@@ -19161,13 +19161,13 @@
         <v>4.78</v>
       </c>
       <c r="Q237" t="n">
-        <v>-10.382</v>
+        <v>-11.429</v>
       </c>
       <c r="R237" t="n">
-        <v>-1038.2</v>
+        <v>-1142.9</v>
       </c>
       <c r="S237" t="n">
-        <v>90.7</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="238">
@@ -19240,13 +19240,13 @@
         <v>3.82</v>
       </c>
       <c r="Q238" t="n">
-        <v>-10.344</v>
+        <v>-11.391</v>
       </c>
       <c r="R238" t="n">
-        <v>-1034.4</v>
+        <v>-1139.1</v>
       </c>
       <c r="S238" t="n">
-        <v>90.7</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="239">
@@ -19319,13 +19319,13 @@
         <v>5.73</v>
       </c>
       <c r="Q239" t="n">
-        <v>-10.286</v>
+        <v>-11.334</v>
       </c>
       <c r="R239" t="n">
-        <v>-1028.6</v>
+        <v>-1133.4</v>
       </c>
       <c r="S239" t="n">
-        <v>90.8</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="240">
@@ -19349,27 +19349,27 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>El Daklyeh</t>
+          <t>Abu Qir Semad</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Maleyeit Kafr El Zayiat</t>
+          <t>La Viena</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>El Daklyeh</t>
+          <t>La Viena</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Maleyeit Kafr El Zayiat</t>
+          <t>Abu Qir Semad</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J240" t="n">
@@ -19384,18 +19384,18 @@
         </is>
       </c>
       <c r="M240" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="O240" t="n">
-        <v>-1</v>
+        <v>0.0478</v>
       </c>
       <c r="P240" t="n">
-        <v>-100</v>
+        <v>4.78</v>
       </c>
       <c r="Q240" t="n">
         <v>-11.286</v>
@@ -19477,10 +19477,10 @@
         <v>2.87</v>
       </c>
       <c r="Q241" t="n">
-        <v>-11.258</v>
+        <v>-11.257</v>
       </c>
       <c r="R241" t="n">
-        <v>-1125.8</v>
+        <v>-1125.7</v>
       </c>
       <c r="S241" t="n">
         <v>90.40000000000001</v>
@@ -20504,10 +20504,10 @@
         <v>1.91</v>
       </c>
       <c r="Q254" t="n">
-        <v>-10.637</v>
+        <v>-10.636</v>
       </c>
       <c r="R254" t="n">
-        <v>-1063.7</v>
+        <v>-1063.6</v>
       </c>
       <c r="S254" t="n">
         <v>90.90000000000001</v>
@@ -21136,10 +21136,10 @@
         <v>5.73</v>
       </c>
       <c r="Q262" t="n">
-        <v>-10.236</v>
+        <v>-10.235</v>
       </c>
       <c r="R262" t="n">
-        <v>-1023.6</v>
+        <v>-1023.5</v>
       </c>
       <c r="S262" t="n">
         <v>91.2</v>
@@ -22637,10 +22637,10 @@
         <v>9.550000000000001</v>
       </c>
       <c r="Q281" t="n">
-        <v>-9.166</v>
+        <v>-9.164999999999999</v>
       </c>
       <c r="R281" t="n">
-        <v>-916.6</v>
+        <v>-916.5</v>
       </c>
       <c r="S281" t="n">
         <v>91.8</v>
@@ -24326,34 +24326,34 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>San Martin T.</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>San Martin T.</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Ciudad Bolivar</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J303" t="n">
         <v>1.05</v>
       </c>
       <c r="K303" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="L303" t="inlineStr">
         <is>
@@ -24361,7 +24361,7 @@
         </is>
       </c>
       <c r="M303" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N303" t="inlineStr">
         <is>
@@ -24369,16 +24369,16 @@
         </is>
       </c>
       <c r="O303" t="n">
-        <v>0.0382</v>
+        <v>0.0478</v>
       </c>
       <c r="P303" t="n">
-        <v>3.82</v>
+        <v>4.78</v>
       </c>
       <c r="Q303" t="n">
-        <v>-9.923999999999999</v>
+        <v>-9.914</v>
       </c>
       <c r="R303" t="n">
-        <v>-992.4</v>
+        <v>-991.4</v>
       </c>
       <c r="S303" t="n">
         <v>91.7</v>
@@ -24454,10 +24454,10 @@
         <v>3.82</v>
       </c>
       <c r="Q304" t="n">
-        <v>-9.885</v>
+        <v>-9.875999999999999</v>
       </c>
       <c r="R304" t="n">
-        <v>-988.5</v>
+        <v>-987.6</v>
       </c>
       <c r="S304" t="n">
         <v>91.7</v>
@@ -24533,10 +24533,10 @@
         <v>9.550000000000001</v>
       </c>
       <c r="Q305" t="n">
-        <v>-9.789999999999999</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="R305" t="n">
-        <v>-979</v>
+        <v>-978</v>
       </c>
       <c r="S305" t="n">
         <v>91.8</v>
@@ -24612,10 +24612,10 @@
         <v>-100</v>
       </c>
       <c r="Q306" t="n">
-        <v>-10.79</v>
+        <v>-10.78</v>
       </c>
       <c r="R306" t="n">
-        <v>-1079</v>
+        <v>-1078</v>
       </c>
       <c r="S306" t="n">
         <v>91.5</v>
@@ -24691,10 +24691,10 @@
         <v>5.73</v>
       </c>
       <c r="Q307" t="n">
-        <v>-10.733</v>
+        <v>-10.723</v>
       </c>
       <c r="R307" t="n">
-        <v>-1073.3</v>
+        <v>-1072.3</v>
       </c>
       <c r="S307" t="n">
         <v>91.5</v>
@@ -24770,10 +24770,10 @@
         <v>7.64</v>
       </c>
       <c r="Q308" t="n">
-        <v>-10.656</v>
+        <v>-10.646</v>
       </c>
       <c r="R308" t="n">
-        <v>-1065.6</v>
+        <v>-1064.6</v>
       </c>
       <c r="S308" t="n">
         <v>91.5</v>
@@ -24849,10 +24849,10 @@
         <v>8.6</v>
       </c>
       <c r="Q309" t="n">
-        <v>-10.57</v>
+        <v>-10.56</v>
       </c>
       <c r="R309" t="n">
-        <v>-1057</v>
+        <v>-1056</v>
       </c>
       <c r="S309" t="n">
         <v>91.59999999999999</v>
@@ -24928,10 +24928,10 @@
         <v>5.73</v>
       </c>
       <c r="Q310" t="n">
-        <v>-10.513</v>
+        <v>-10.503</v>
       </c>
       <c r="R310" t="n">
-        <v>-1051.3</v>
+        <v>-1050.3</v>
       </c>
       <c r="S310" t="n">
         <v>91.59999999999999</v>
@@ -25007,10 +25007,10 @@
         <v>5.73</v>
       </c>
       <c r="Q311" t="n">
-        <v>-10.456</v>
+        <v>-10.446</v>
       </c>
       <c r="R311" t="n">
-        <v>-1045.6</v>
+        <v>-1044.6</v>
       </c>
       <c r="S311" t="n">
         <v>91.59999999999999</v>
@@ -25086,10 +25086,10 @@
         <v>7.64</v>
       </c>
       <c r="Q312" t="n">
-        <v>-10.379</v>
+        <v>-10.369</v>
       </c>
       <c r="R312" t="n">
-        <v>-1037.9</v>
+        <v>-1036.9</v>
       </c>
       <c r="S312" t="n">
         <v>91.59999999999999</v>
@@ -25165,10 +25165,10 @@
         <v>3.82</v>
       </c>
       <c r="Q313" t="n">
-        <v>-10.341</v>
+        <v>-10.331</v>
       </c>
       <c r="R313" t="n">
-        <v>-1034.1</v>
+        <v>-1033.1</v>
       </c>
       <c r="S313" t="n">
         <v>91.7</v>
@@ -25244,10 +25244,10 @@
         <v>5.73</v>
       </c>
       <c r="Q314" t="n">
-        <v>-10.284</v>
+        <v>-10.274</v>
       </c>
       <c r="R314" t="n">
-        <v>-1028.4</v>
+        <v>-1027.4</v>
       </c>
       <c r="S314" t="n">
         <v>91.7</v>
@@ -25323,10 +25323,10 @@
         <v>5.73</v>
       </c>
       <c r="Q315" t="n">
-        <v>-10.226</v>
+        <v>-10.217</v>
       </c>
       <c r="R315" t="n">
-        <v>-1022.6</v>
+        <v>-1021.7</v>
       </c>
       <c r="S315" t="n">
         <v>91.7</v>
@@ -25402,10 +25402,10 @@
         <v>7.64</v>
       </c>
       <c r="Q316" t="n">
-        <v>-10.15</v>
+        <v>-10.14</v>
       </c>
       <c r="R316" t="n">
-        <v>-1015</v>
+        <v>-1014</v>
       </c>
       <c r="S316" t="n">
         <v>91.7</v>
@@ -25432,27 +25432,27 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Vila Nova FC</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atletico GO</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atletico GO</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Vila Nova FC</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J317" t="n">
@@ -25467,7 +25467,7 @@
         </is>
       </c>
       <c r="M317" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N317" t="inlineStr">
         <is>
@@ -25475,16 +25475,16 @@
         </is>
       </c>
       <c r="O317" t="n">
-        <v>0.0573</v>
+        <v>0.0764</v>
       </c>
       <c r="P317" t="n">
-        <v>5.73</v>
+        <v>7.64</v>
       </c>
       <c r="Q317" t="n">
-        <v>-10.093</v>
+        <v>-10.064</v>
       </c>
       <c r="R317" t="n">
-        <v>-1009.3</v>
+        <v>-1006.4</v>
       </c>
       <c r="S317" t="n">
         <v>91.8</v>
@@ -25511,27 +25511,27 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Vila Nova FC</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Vila Nova FC</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J318" t="n">
@@ -25546,7 +25546,7 @@
         </is>
       </c>
       <c r="M318" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N318" t="inlineStr">
         <is>
@@ -25554,16 +25554,16 @@
         </is>
       </c>
       <c r="O318" t="n">
-        <v>0.0764</v>
+        <v>0.0573</v>
       </c>
       <c r="P318" t="n">
-        <v>7.64</v>
+        <v>5.73</v>
       </c>
       <c r="Q318" t="n">
-        <v>-10.016</v>
+        <v>-10.007</v>
       </c>
       <c r="R318" t="n">
-        <v>-1001.6</v>
+        <v>-1000.7</v>
       </c>
       <c r="S318" t="n">
         <v>91.8</v>
@@ -25639,10 +25639,10 @@
         <v>5.73</v>
       </c>
       <c r="Q319" t="n">
-        <v>-9.959</v>
+        <v>-9.949</v>
       </c>
       <c r="R319" t="n">
-        <v>-995.9</v>
+        <v>-994.9</v>
       </c>
       <c r="S319" t="n">
         <v>91.8</v>
@@ -25718,10 +25718,10 @@
         <v>2.87</v>
       </c>
       <c r="Q320" t="n">
-        <v>-9.93</v>
+        <v>-9.920999999999999</v>
       </c>
       <c r="R320" t="n">
-        <v>-993</v>
+        <v>-992.1</v>
       </c>
       <c r="S320" t="n">
         <v>91.8</v>
@@ -25797,10 +25797,10 @@
         <v>3.82</v>
       </c>
       <c r="Q321" t="n">
-        <v>-9.891999999999999</v>
+        <v>-9.882</v>
       </c>
       <c r="R321" t="n">
-        <v>-989.2</v>
+        <v>-988.2</v>
       </c>
       <c r="S321" t="n">
         <v>91.90000000000001</v>
@@ -25876,10 +25876,10 @@
         <v>3.82</v>
       </c>
       <c r="Q322" t="n">
-        <v>-9.853999999999999</v>
+        <v>-9.843999999999999</v>
       </c>
       <c r="R322" t="n">
-        <v>-985.4</v>
+        <v>-984.4</v>
       </c>
       <c r="S322" t="n">
         <v>91.90000000000001</v>
@@ -25955,10 +25955,10 @@
         <v>9.550000000000001</v>
       </c>
       <c r="Q323" t="n">
-        <v>-9.757999999999999</v>
+        <v>-9.749000000000001</v>
       </c>
       <c r="R323" t="n">
-        <v>-975.8</v>
+        <v>-974.9</v>
       </c>
       <c r="S323" t="n">
         <v>91.90000000000001</v>
@@ -26034,10 +26034,10 @@
         <v>7.64</v>
       </c>
       <c r="Q324" t="n">
-        <v>-9.682</v>
+        <v>-9.672000000000001</v>
       </c>
       <c r="R324" t="n">
-        <v>-968.2</v>
+        <v>-967.2</v>
       </c>
       <c r="S324" t="n">
         <v>92</v>
@@ -26113,10 +26113,10 @@
         <v>4.78</v>
       </c>
       <c r="Q325" t="n">
-        <v>-9.634</v>
+        <v>-9.624000000000001</v>
       </c>
       <c r="R325" t="n">
-        <v>-963.4</v>
+        <v>-962.4</v>
       </c>
       <c r="S325" t="n">
         <v>92</v>
@@ -26192,10 +26192,10 @@
         <v>6.69</v>
       </c>
       <c r="Q326" t="n">
-        <v>-9.567</v>
+        <v>-9.558</v>
       </c>
       <c r="R326" t="n">
-        <v>-956.7</v>
+        <v>-955.8</v>
       </c>
       <c r="S326" t="n">
         <v>92</v>
@@ -26271,10 +26271,10 @@
         <v>4.78</v>
       </c>
       <c r="Q327" t="n">
-        <v>-9.52</v>
+        <v>-9.51</v>
       </c>
       <c r="R327" t="n">
-        <v>-952</v>
+        <v>-951</v>
       </c>
       <c r="S327" t="n">
         <v>92</v>
@@ -26350,10 +26350,10 @@
         <v>4.78</v>
       </c>
       <c r="Q328" t="n">
-        <v>-9.472</v>
+        <v>-9.462</v>
       </c>
       <c r="R328" t="n">
-        <v>-947.2</v>
+        <v>-946.2</v>
       </c>
       <c r="S328" t="n">
         <v>92</v>
@@ -26429,10 +26429,10 @@
         <v>3.82</v>
       </c>
       <c r="Q329" t="n">
-        <v>-9.433999999999999</v>
+        <v>-9.423999999999999</v>
       </c>
       <c r="R329" t="n">
-        <v>-943.4</v>
+        <v>-942.4</v>
       </c>
       <c r="S329" t="n">
         <v>92.09999999999999</v>
@@ -26508,10 +26508,10 @@
         <v>3.82</v>
       </c>
       <c r="Q330" t="n">
-        <v>-9.395</v>
+        <v>-9.385999999999999</v>
       </c>
       <c r="R330" t="n">
-        <v>-939.5</v>
+        <v>-938.6</v>
       </c>
       <c r="S330" t="n">
         <v>92.09999999999999</v>
@@ -26587,10 +26587,10 @@
         <v>7.64</v>
       </c>
       <c r="Q331" t="n">
-        <v>-9.319000000000001</v>
+        <v>-9.308999999999999</v>
       </c>
       <c r="R331" t="n">
-        <v>-931.9</v>
+        <v>-930.9</v>
       </c>
       <c r="S331" t="n">
         <v>92.09999999999999</v>
@@ -26666,10 +26666,10 @@
         <v>7.64</v>
       </c>
       <c r="Q332" t="n">
-        <v>-9.243</v>
+        <v>-9.233000000000001</v>
       </c>
       <c r="R332" t="n">
-        <v>-924.3</v>
+        <v>-923.3</v>
       </c>
       <c r="S332" t="n">
         <v>92.09999999999999</v>
@@ -26745,10 +26745,10 @@
         <v>6.69</v>
       </c>
       <c r="Q333" t="n">
-        <v>-9.176</v>
+        <v>-9.166</v>
       </c>
       <c r="R333" t="n">
-        <v>-917.6</v>
+        <v>-916.6</v>
       </c>
       <c r="S333" t="n">
         <v>92.2</v>
@@ -26824,10 +26824,10 @@
         <v>4.78</v>
       </c>
       <c r="Q334" t="n">
-        <v>-9.128</v>
+        <v>-9.118</v>
       </c>
       <c r="R334" t="n">
-        <v>-912.8</v>
+        <v>-911.8</v>
       </c>
       <c r="S334" t="n">
         <v>92.2</v>
@@ -26903,10 +26903,10 @@
         <v>10.51</v>
       </c>
       <c r="Q335" t="n">
-        <v>-9.023</v>
+        <v>-9.013</v>
       </c>
       <c r="R335" t="n">
-        <v>-902.3</v>
+        <v>-901.3</v>
       </c>
       <c r="S335" t="n">
         <v>92.2</v>
@@ -26982,10 +26982,10 @@
         <v>8.6</v>
       </c>
       <c r="Q336" t="n">
-        <v>-8.936999999999999</v>
+        <v>-8.927</v>
       </c>
       <c r="R336" t="n">
-        <v>-893.7</v>
+        <v>-892.7</v>
       </c>
       <c r="S336" t="n">
         <v>92.2</v>
@@ -27061,10 +27061,10 @@
         <v>5.73</v>
       </c>
       <c r="Q337" t="n">
-        <v>-8.879</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="R337" t="n">
-        <v>-887.9</v>
+        <v>-887</v>
       </c>
       <c r="S337" t="n">
         <v>92.3</v>
@@ -27140,10 +27140,10 @@
         <v>8.6</v>
       </c>
       <c r="Q338" t="n">
-        <v>-8.792999999999999</v>
+        <v>-8.784000000000001</v>
       </c>
       <c r="R338" t="n">
-        <v>-879.3</v>
+        <v>-878.4</v>
       </c>
       <c r="S338" t="n">
         <v>92.3</v>
@@ -27219,10 +27219,10 @@
         <v>4.78</v>
       </c>
       <c r="Q339" t="n">
-        <v>-8.746</v>
+        <v>-8.736000000000001</v>
       </c>
       <c r="R339" t="n">
-        <v>-874.6</v>
+        <v>-873.6</v>
       </c>
       <c r="S339" t="n">
         <v>92.3</v>
@@ -27298,10 +27298,10 @@
         <v>3.82</v>
       </c>
       <c r="Q340" t="n">
-        <v>-8.707000000000001</v>
+        <v>-8.698</v>
       </c>
       <c r="R340" t="n">
-        <v>-870.7</v>
+        <v>-869.8</v>
       </c>
       <c r="S340" t="n">
         <v>92.3</v>
@@ -27377,10 +27377,10 @@
         <v>10.51</v>
       </c>
       <c r="Q341" t="n">
-        <v>-8.602</v>
+        <v>-8.593</v>
       </c>
       <c r="R341" t="n">
-        <v>-860.2</v>
+        <v>-859.3</v>
       </c>
       <c r="S341" t="n">
         <v>92.40000000000001</v>
@@ -27456,10 +27456,10 @@
         <v>3.82</v>
       </c>
       <c r="Q342" t="n">
-        <v>-8.564</v>
+        <v>-8.554</v>
       </c>
       <c r="R342" t="n">
-        <v>-856.4</v>
+        <v>-855.4</v>
       </c>
       <c r="S342" t="n">
         <v>92.40000000000001</v>
@@ -27535,10 +27535,10 @@
         <v>7.64</v>
       </c>
       <c r="Q343" t="n">
-        <v>-8.488</v>
+        <v>-8.478</v>
       </c>
       <c r="R343" t="n">
-        <v>-848.8</v>
+        <v>-847.8</v>
       </c>
       <c r="S343" t="n">
         <v>92.40000000000001</v>
@@ -27614,10 +27614,10 @@
         <v>9.550000000000001</v>
       </c>
       <c r="Q344" t="n">
-        <v>-8.391999999999999</v>
+        <v>-8.382</v>
       </c>
       <c r="R344" t="n">
-        <v>-839.2</v>
+        <v>-838.2</v>
       </c>
       <c r="S344" t="n">
         <v>92.40000000000001</v>
@@ -27693,10 +27693,10 @@
         <v>-100</v>
       </c>
       <c r="Q345" t="n">
-        <v>-9.391999999999999</v>
+        <v>-9.382</v>
       </c>
       <c r="R345" t="n">
-        <v>-939.2</v>
+        <v>-938.2</v>
       </c>
       <c r="S345" t="n">
         <v>92.2</v>
@@ -27772,10 +27772,10 @@
         <v>9.550000000000001</v>
       </c>
       <c r="Q346" t="n">
-        <v>-9.297000000000001</v>
+        <v>-9.287000000000001</v>
       </c>
       <c r="R346" t="n">
-        <v>-929.7</v>
+        <v>-928.7</v>
       </c>
       <c r="S346" t="n">
         <v>92.2</v>
@@ -27851,10 +27851,10 @@
         <v>3.82</v>
       </c>
       <c r="Q347" t="n">
-        <v>-9.259</v>
+        <v>-9.249000000000001</v>
       </c>
       <c r="R347" t="n">
-        <v>-925.9</v>
+        <v>-924.9</v>
       </c>
       <c r="S347" t="n">
         <v>92.2</v>
@@ -27930,10 +27930,10 @@
         <v>4.78</v>
       </c>
       <c r="Q348" t="n">
-        <v>-9.211</v>
+        <v>-9.201000000000001</v>
       </c>
       <c r="R348" t="n">
-        <v>-921.1</v>
+        <v>-920.1</v>
       </c>
       <c r="S348" t="n">
         <v>92.2</v>
@@ -28009,10 +28009,10 @@
         <v>8.6</v>
       </c>
       <c r="Q349" t="n">
-        <v>-9.125</v>
+        <v>-9.115</v>
       </c>
       <c r="R349" t="n">
-        <v>-912.5</v>
+        <v>-911.5</v>
       </c>
       <c r="S349" t="n">
         <v>92.2</v>
@@ -28088,10 +28088,10 @@
         <v>3.82</v>
       </c>
       <c r="Q350" t="n">
-        <v>-9.087</v>
+        <v>-9.077</v>
       </c>
       <c r="R350" t="n">
-        <v>-908.7</v>
+        <v>-907.7</v>
       </c>
       <c r="S350" t="n">
         <v>92.3</v>
@@ -28167,10 +28167,10 @@
         <v>6.69</v>
       </c>
       <c r="Q351" t="n">
-        <v>-9.02</v>
+        <v>-9.01</v>
       </c>
       <c r="R351" t="n">
-        <v>-902</v>
+        <v>-901</v>
       </c>
       <c r="S351" t="n">
         <v>92.3</v>
@@ -28197,34 +28197,34 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Villa Mitre</t>
+          <t>Circulo Deportivo</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Olimpo Bahia Blanca</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Circulo Deportivo</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Villa Mitre</t>
+          <t>Olimpo Bahia Blanca</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J352" t="n">
         <v>1</v>
       </c>
       <c r="K352" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="L352" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         </is>
       </c>
       <c r="M352" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N352" t="inlineStr">
         <is>
@@ -28240,16 +28240,16 @@
         </is>
       </c>
       <c r="O352" t="n">
-        <v>0.0191</v>
+        <v>0.0382</v>
       </c>
       <c r="P352" t="n">
-        <v>1.91</v>
+        <v>3.82</v>
       </c>
       <c r="Q352" t="n">
-        <v>-9.000999999999999</v>
+        <v>-8.972</v>
       </c>
       <c r="R352" t="n">
-        <v>-900.1</v>
+        <v>-897.2</v>
       </c>
       <c r="S352" t="n">
         <v>92.3</v>
@@ -28276,34 +28276,34 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Circulo Deportivo</t>
+          <t>Villa Mitre</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Olimpo Bahia Blanca</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Circulo Deportivo</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Olimpo Bahia Blanca</t>
+          <t>Villa Mitre</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="J353" t="n">
         <v>1</v>
       </c>
       <c r="K353" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="L353" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         </is>
       </c>
       <c r="M353" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N353" t="inlineStr">
         <is>
@@ -28319,16 +28319,16 @@
         </is>
       </c>
       <c r="O353" t="n">
-        <v>0.0382</v>
+        <v>0.0191</v>
       </c>
       <c r="P353" t="n">
-        <v>3.82</v>
+        <v>1.91</v>
       </c>
       <c r="Q353" t="n">
-        <v>-8.962</v>
+        <v>-8.952999999999999</v>
       </c>
       <c r="R353" t="n">
-        <v>-896.2</v>
+        <v>-895.3</v>
       </c>
       <c r="S353" t="n">
         <v>92.3</v>
@@ -28404,10 +28404,10 @@
         <v>7.64</v>
       </c>
       <c r="Q354" t="n">
-        <v>-8.885999999999999</v>
+        <v>-8.875999999999999</v>
       </c>
       <c r="R354" t="n">
-        <v>-888.6</v>
+        <v>-887.6</v>
       </c>
       <c r="S354" t="n">
         <v>92.40000000000001</v>
@@ -28483,10 +28483,10 @@
         <v>9.550000000000001</v>
       </c>
       <c r="Q355" t="n">
-        <v>-8.789999999999999</v>
+        <v>-8.781000000000001</v>
       </c>
       <c r="R355" t="n">
-        <v>-879</v>
+        <v>-878.1</v>
       </c>
       <c r="S355" t="n">
         <v>92.40000000000001</v>
@@ -28562,10 +28562,10 @@
         <v>4.78</v>
       </c>
       <c r="Q356" t="n">
-        <v>-8.743</v>
+        <v>-8.733000000000001</v>
       </c>
       <c r="R356" t="n">
-        <v>-874.3</v>
+        <v>-873.3</v>
       </c>
       <c r="S356" t="n">
         <v>92.40000000000001</v>
@@ -28641,10 +28641,10 @@
         <v>5.73</v>
       </c>
       <c r="Q357" t="n">
-        <v>-8.685</v>
+        <v>-8.676</v>
       </c>
       <c r="R357" t="n">
-        <v>-868.5</v>
+        <v>-867.6</v>
       </c>
       <c r="S357" t="n">
         <v>92.40000000000001</v>
@@ -28720,10 +28720,10 @@
         <v>10.51</v>
       </c>
       <c r="Q358" t="n">
-        <v>-8.58</v>
+        <v>-8.57</v>
       </c>
       <c r="R358" t="n">
-        <v>-858</v>
+        <v>-857</v>
       </c>
       <c r="S358" t="n">
         <v>92.40000000000001</v>
@@ -28799,10 +28799,10 @@
         <v>10.51</v>
       </c>
       <c r="Q359" t="n">
-        <v>-8.475</v>
+        <v>-8.465</v>
       </c>
       <c r="R359" t="n">
-        <v>-847.5</v>
+        <v>-846.5</v>
       </c>
       <c r="S359" t="n">
         <v>92.5</v>
@@ -28878,10 +28878,10 @@
         <v>7.64</v>
       </c>
       <c r="Q360" t="n">
-        <v>-8.398999999999999</v>
+        <v>-8.388999999999999</v>
       </c>
       <c r="R360" t="n">
-        <v>-839.9</v>
+        <v>-838.9</v>
       </c>
       <c r="S360" t="n">
         <v>92.5</v>
@@ -28957,10 +28957,10 @@
         <v>5.73</v>
       </c>
       <c r="Q361" t="n">
-        <v>-8.340999999999999</v>
+        <v>-8.332000000000001</v>
       </c>
       <c r="R361" t="n">
-        <v>-834.1</v>
+        <v>-833.2</v>
       </c>
       <c r="S361" t="n">
         <v>92.5</v>
@@ -29036,10 +29036,10 @@
         <v>3.82</v>
       </c>
       <c r="Q362" t="n">
-        <v>-8.303000000000001</v>
+        <v>-8.292999999999999</v>
       </c>
       <c r="R362" t="n">
-        <v>-830.3</v>
+        <v>-829.3</v>
       </c>
       <c r="S362" t="n">
         <v>92.5</v>
@@ -29115,10 +29115,10 @@
         <v>5.73</v>
       </c>
       <c r="Q363" t="n">
-        <v>-8.246</v>
+        <v>-8.236000000000001</v>
       </c>
       <c r="R363" t="n">
-        <v>-824.6</v>
+        <v>-823.6</v>
       </c>
       <c r="S363" t="n">
         <v>92.5</v>
@@ -29194,10 +29194,10 @@
         <v>3.82</v>
       </c>
       <c r="Q364" t="n">
-        <v>-8.208</v>
+        <v>-8.198</v>
       </c>
       <c r="R364" t="n">
-        <v>-820.8</v>
+        <v>-819.8</v>
       </c>
       <c r="S364" t="n">
         <v>92.59999999999999</v>
@@ -29273,10 +29273,10 @@
         <v>3.82</v>
       </c>
       <c r="Q365" t="n">
-        <v>-8.17</v>
+        <v>-8.16</v>
       </c>
       <c r="R365" t="n">
-        <v>-817</v>
+        <v>-816</v>
       </c>
       <c r="S365" t="n">
         <v>92.59999999999999</v>
@@ -29352,10 +29352,10 @@
         <v>6.69</v>
       </c>
       <c r="Q366" t="n">
-        <v>-8.103</v>
+        <v>-8.093</v>
       </c>
       <c r="R366" t="n">
-        <v>-810.3</v>
+        <v>-809.3</v>
       </c>
       <c r="S366" t="n">
         <v>92.59999999999999</v>
@@ -29431,10 +29431,10 @@
         <v>7.64</v>
       </c>
       <c r="Q367" t="n">
-        <v>-8.026</v>
+        <v>-8.016</v>
       </c>
       <c r="R367" t="n">
-        <v>-802.6</v>
+        <v>-801.6</v>
       </c>
       <c r="S367" t="n">
         <v>92.59999999999999</v>
@@ -29510,10 +29510,10 @@
         <v>7.64</v>
       </c>
       <c r="Q368" t="n">
-        <v>-7.95</v>
+        <v>-7.94</v>
       </c>
       <c r="R368" t="n">
-        <v>-795</v>
+        <v>-794</v>
       </c>
       <c r="S368" t="n">
         <v>92.59999999999999</v>
@@ -29589,10 +29589,10 @@
         <v>5.73</v>
       </c>
       <c r="Q369" t="n">
-        <v>-7.893</v>
+        <v>-7.883</v>
       </c>
       <c r="R369" t="n">
-        <v>-789.3</v>
+        <v>-788.3</v>
       </c>
       <c r="S369" t="n">
         <v>92.7</v>
@@ -29668,10 +29668,10 @@
         <v>6.69</v>
       </c>
       <c r="Q370" t="n">
-        <v>-7.826</v>
+        <v>-7.816</v>
       </c>
       <c r="R370" t="n">
-        <v>-782.6</v>
+        <v>-781.6</v>
       </c>
       <c r="S370" t="n">
         <v>92.7</v>
@@ -29747,10 +29747,10 @@
         <v>4.78</v>
       </c>
       <c r="Q371" t="n">
-        <v>-7.778</v>
+        <v>-7.768</v>
       </c>
       <c r="R371" t="n">
-        <v>-777.8</v>
+        <v>-776.8</v>
       </c>
       <c r="S371" t="n">
         <v>92.7</v>
@@ -29826,10 +29826,10 @@
         <v>10.51</v>
       </c>
       <c r="Q372" t="n">
-        <v>-7.673</v>
+        <v>-7.663</v>
       </c>
       <c r="R372" t="n">
-        <v>-767.3</v>
+        <v>-766.3</v>
       </c>
       <c r="S372" t="n">
         <v>92.7</v>
@@ -29905,10 +29905,10 @@
         <v>9.550000000000001</v>
       </c>
       <c r="Q373" t="n">
-        <v>-7.577</v>
+        <v>-7.567</v>
       </c>
       <c r="R373" t="n">
-        <v>-757.7</v>
+        <v>-756.7</v>
       </c>
       <c r="S373" t="n">
         <v>92.7</v>
@@ -29984,10 +29984,10 @@
         <v>7.64</v>
       </c>
       <c r="Q374" t="n">
-        <v>-7.501</v>
+        <v>-7.491</v>
       </c>
       <c r="R374" t="n">
-        <v>-750.1</v>
+        <v>-749.1</v>
       </c>
       <c r="S374" t="n">
         <v>92.8</v>
@@ -30063,10 +30063,10 @@
         <v>5.73</v>
       </c>
       <c r="Q375" t="n">
-        <v>-7.444</v>
+        <v>-7.434</v>
       </c>
       <c r="R375" t="n">
-        <v>-744.4</v>
+        <v>-743.4</v>
       </c>
       <c r="S375" t="n">
         <v>92.8</v>
@@ -30142,10 +30142,10 @@
         <v>3.82</v>
       </c>
       <c r="Q376" t="n">
-        <v>-7.405</v>
+        <v>-7.396</v>
       </c>
       <c r="R376" t="n">
-        <v>-740.5</v>
+        <v>-739.6</v>
       </c>
       <c r="S376" t="n">
         <v>92.8</v>
@@ -30221,10 +30221,10 @@
         <v>3.82</v>
       </c>
       <c r="Q377" t="n">
-        <v>-7.367</v>
+        <v>-7.357</v>
       </c>
       <c r="R377" t="n">
-        <v>-736.7</v>
+        <v>-735.7</v>
       </c>
       <c r="S377" t="n">
         <v>92.8</v>
@@ -30300,10 +30300,10 @@
         <v>6.69</v>
       </c>
       <c r="Q378" t="n">
-        <v>-7.3</v>
+        <v>-7.29</v>
       </c>
       <c r="R378" t="n">
-        <v>-730</v>
+        <v>-729</v>
       </c>
       <c r="S378" t="n">
         <v>92.8</v>
@@ -30379,10 +30379,10 @@
         <v>7.64</v>
       </c>
       <c r="Q379" t="n">
-        <v>-7.224</v>
+        <v>-7.214</v>
       </c>
       <c r="R379" t="n">
-        <v>-722.4</v>
+        <v>-721.4</v>
       </c>
       <c r="S379" t="n">
         <v>92.90000000000001</v>
@@ -30458,10 +30458,10 @@
         <v>2.87</v>
       </c>
       <c r="Q380" t="n">
-        <v>-7.195</v>
+        <v>-7.185</v>
       </c>
       <c r="R380" t="n">
-        <v>-719.5</v>
+        <v>-718.5</v>
       </c>
       <c r="S380" t="n">
         <v>92.90000000000001</v>
@@ -30537,10 +30537,10 @@
         <v>7.64</v>
       </c>
       <c r="Q381" t="n">
-        <v>-7.119</v>
+        <v>-7.109</v>
       </c>
       <c r="R381" t="n">
-        <v>-711.9</v>
+        <v>-710.9</v>
       </c>
       <c r="S381" t="n">
         <v>92.90000000000001</v>
@@ -30616,10 +30616,10 @@
         <v>6.69</v>
       </c>
       <c r="Q382" t="n">
-        <v>-7.052</v>
+        <v>-7.042</v>
       </c>
       <c r="R382" t="n">
-        <v>-705.2</v>
+        <v>-704.2</v>
       </c>
       <c r="S382" t="n">
         <v>92.90000000000001</v>
@@ -30695,10 +30695,10 @@
         <v>7.64</v>
       </c>
       <c r="Q383" t="n">
-        <v>-6.975</v>
+        <v>-6.966</v>
       </c>
       <c r="R383" t="n">
-        <v>-697.5</v>
+        <v>-696.6</v>
       </c>
       <c r="S383" t="n">
         <v>92.90000000000001</v>
@@ -30774,10 +30774,10 @@
         <v>5.73</v>
       </c>
       <c r="Q384" t="n">
-        <v>-6.918</v>
+        <v>-6.908</v>
       </c>
       <c r="R384" t="n">
-        <v>-691.8</v>
+        <v>-690.8</v>
       </c>
       <c r="S384" t="n">
         <v>93</v>
@@ -30853,10 +30853,10 @@
         <v>4.78</v>
       </c>
       <c r="Q385" t="n">
-        <v>-6.87</v>
+        <v>-6.861</v>
       </c>
       <c r="R385" t="n">
-        <v>-687</v>
+        <v>-686.1</v>
       </c>
       <c r="S385" t="n">
         <v>93</v>
@@ -30932,10 +30932,10 @@
         <v>3.82</v>
       </c>
       <c r="Q386" t="n">
-        <v>-6.832</v>
+        <v>-6.822</v>
       </c>
       <c r="R386" t="n">
-        <v>-683.2</v>
+        <v>-682.2</v>
       </c>
       <c r="S386" t="n">
         <v>93</v>
@@ -31011,10 +31011,10 @@
         <v>4.78</v>
       </c>
       <c r="Q387" t="n">
-        <v>-6.784</v>
+        <v>-6.775</v>
       </c>
       <c r="R387" t="n">
-        <v>-678.4</v>
+        <v>-677.5</v>
       </c>
       <c r="S387" t="n">
         <v>93</v>
@@ -31090,10 +31090,10 @@
         <v>7.64</v>
       </c>
       <c r="Q388" t="n">
-        <v>-6.708</v>
+        <v>-6.698</v>
       </c>
       <c r="R388" t="n">
-        <v>-670.8</v>
+        <v>-669.8</v>
       </c>
       <c r="S388" t="n">
         <v>93</v>
@@ -31169,10 +31169,10 @@
         <v>5.73</v>
       </c>
       <c r="Q389" t="n">
-        <v>-6.651</v>
+        <v>-6.641</v>
       </c>
       <c r="R389" t="n">
-        <v>-665.1</v>
+        <v>-664.1</v>
       </c>
       <c r="S389" t="n">
         <v>93</v>
@@ -31248,10 +31248,10 @@
         <v>3.82</v>
       </c>
       <c r="Q390" t="n">
-        <v>-6.612</v>
+        <v>-6.603</v>
       </c>
       <c r="R390" t="n">
-        <v>-661.2</v>
+        <v>-660.3</v>
       </c>
       <c r="S390" t="n">
         <v>93.09999999999999</v>
@@ -31327,10 +31327,10 @@
         <v>6.69</v>
       </c>
       <c r="Q391" t="n">
-        <v>-6.546</v>
+        <v>-6.536</v>
       </c>
       <c r="R391" t="n">
-        <v>-654.6</v>
+        <v>-653.6</v>
       </c>
       <c r="S391" t="n">
         <v>93.09999999999999</v>
@@ -31406,10 +31406,10 @@
         <v>3.82</v>
       </c>
       <c r="Q392" t="n">
-        <v>-6.507</v>
+        <v>-6.498</v>
       </c>
       <c r="R392" t="n">
-        <v>-650.7</v>
+        <v>-649.8</v>
       </c>
       <c r="S392" t="n">
         <v>93.09999999999999</v>
@@ -31485,10 +31485,10 @@
         <v>8.6</v>
       </c>
       <c r="Q393" t="n">
-        <v>-6.421</v>
+        <v>-6.412</v>
       </c>
       <c r="R393" t="n">
-        <v>-642.1</v>
+        <v>-641.2</v>
       </c>
       <c r="S393" t="n">
         <v>93.09999999999999</v>
@@ -31564,10 +31564,10 @@
         <v>8.6</v>
       </c>
       <c r="Q394" t="n">
-        <v>-6.335</v>
+        <v>-6.326</v>
       </c>
       <c r="R394" t="n">
-        <v>-633.5</v>
+        <v>-632.6</v>
       </c>
       <c r="S394" t="n">
         <v>93.09999999999999</v>
@@ -31643,10 +31643,10 @@
         <v>-100</v>
       </c>
       <c r="Q395" t="n">
-        <v>-7.335</v>
+        <v>-7.326</v>
       </c>
       <c r="R395" t="n">
-        <v>-733.5</v>
+        <v>-732.6</v>
       </c>
       <c r="S395" t="n">
         <v>92.90000000000001</v>
@@ -31722,10 +31722,10 @@
         <v>5.73</v>
       </c>
       <c r="Q396" t="n">
-        <v>-7.278</v>
+        <v>-7.268</v>
       </c>
       <c r="R396" t="n">
-        <v>-727.8</v>
+        <v>-726.8</v>
       </c>
       <c r="S396" t="n">
         <v>92.90000000000001</v>
@@ -31801,10 +31801,10 @@
         <v>7.64</v>
       </c>
       <c r="Q397" t="n">
-        <v>-7.202</v>
+        <v>-7.192</v>
       </c>
       <c r="R397" t="n">
-        <v>-720.2</v>
+        <v>-719.2</v>
       </c>
       <c r="S397" t="n">
         <v>92.90000000000001</v>
@@ -31880,10 +31880,10 @@
         <v>5.73</v>
       </c>
       <c r="Q398" t="n">
-        <v>-7.144</v>
+        <v>-7.135</v>
       </c>
       <c r="R398" t="n">
-        <v>-714.4</v>
+        <v>-713.5</v>
       </c>
       <c r="S398" t="n">
         <v>92.90000000000001</v>
@@ -31959,10 +31959,10 @@
         <v>3.82</v>
       </c>
       <c r="Q399" t="n">
-        <v>-7.106</v>
+        <v>-7.096</v>
       </c>
       <c r="R399" t="n">
-        <v>-710.6</v>
+        <v>-709.6</v>
       </c>
       <c r="S399" t="n">
         <v>93</v>
@@ -32038,10 +32038,10 @@
         <v>4.78</v>
       </c>
       <c r="Q400" t="n">
-        <v>-7.058</v>
+        <v>-7.049</v>
       </c>
       <c r="R400" t="n">
-        <v>-705.8</v>
+        <v>-704.9</v>
       </c>
       <c r="S400" t="n">
         <v>93</v>
@@ -32117,10 +32117,10 @@
         <v>4.78</v>
       </c>
       <c r="Q401" t="n">
-        <v>-7.011</v>
+        <v>-7.001</v>
       </c>
       <c r="R401" t="n">
-        <v>-701.1</v>
+        <v>-700.1</v>
       </c>
       <c r="S401" t="n">
         <v>93</v>
@@ -32196,10 +32196,10 @@
         <v>3.82</v>
       </c>
       <c r="Q402" t="n">
-        <v>-6.972</v>
+        <v>-6.963</v>
       </c>
       <c r="R402" t="n">
-        <v>-697.2</v>
+        <v>-696.3</v>
       </c>
       <c r="S402" t="n">
         <v>93</v>
@@ -32275,10 +32275,10 @@
         <v>5.73</v>
       </c>
       <c r="Q403" t="n">
-        <v>-6.915</v>
+        <v>-6.905</v>
       </c>
       <c r="R403" t="n">
-        <v>-691.5</v>
+        <v>-690.5</v>
       </c>
       <c r="S403" t="n">
         <v>93</v>
@@ -32354,10 +32354,10 @@
         <v>2.87</v>
       </c>
       <c r="Q404" t="n">
-        <v>-6.886</v>
+        <v>-6.877</v>
       </c>
       <c r="R404" t="n">
-        <v>-688.6</v>
+        <v>-687.7</v>
       </c>
       <c r="S404" t="n">
         <v>93.09999999999999</v>
@@ -32433,10 +32433,10 @@
         <v>4.78</v>
       </c>
       <c r="Q405" t="n">
-        <v>-6.839</v>
+        <v>-6.829</v>
       </c>
       <c r="R405" t="n">
-        <v>-683.9</v>
+        <v>-682.9</v>
       </c>
       <c r="S405" t="n">
         <v>93.09999999999999</v>
@@ -32512,10 +32512,10 @@
         <v>3.82</v>
       </c>
       <c r="Q406" t="n">
-        <v>-6.8</v>
+        <v>-6.791</v>
       </c>
       <c r="R406" t="n">
-        <v>-680</v>
+        <v>-679.1</v>
       </c>
       <c r="S406" t="n">
         <v>93.09999999999999</v>
@@ -32591,10 +32591,10 @@
         <v>4.78</v>
       </c>
       <c r="Q407" t="n">
-        <v>-6.753</v>
+        <v>-6.743</v>
       </c>
       <c r="R407" t="n">
-        <v>-675.3</v>
+        <v>-674.3</v>
       </c>
       <c r="S407" t="n">
         <v>93.09999999999999</v>
@@ -32670,10 +32670,10 @@
         <v>6.69</v>
       </c>
       <c r="Q408" t="n">
-        <v>-6.686</v>
+        <v>-6.676</v>
       </c>
       <c r="R408" t="n">
-        <v>-668.6</v>
+        <v>-667.6</v>
       </c>
       <c r="S408" t="n">
         <v>93.09999999999999</v>
@@ -32749,10 +32749,10 @@
         <v>7.64</v>
       </c>
       <c r="Q409" t="n">
-        <v>-6.609</v>
+        <v>-6.6</v>
       </c>
       <c r="R409" t="n">
-        <v>-660.9</v>
+        <v>-660</v>
       </c>
       <c r="S409" t="n">
         <v>93.09999999999999</v>
@@ -32828,10 +32828,10 @@
         <v>5.73</v>
       </c>
       <c r="Q410" t="n">
-        <v>-6.552</v>
+        <v>-6.542</v>
       </c>
       <c r="R410" t="n">
-        <v>-655.2</v>
+        <v>-654.2</v>
       </c>
       <c r="S410" t="n">
         <v>93.2</v>
@@ -32907,10 +32907,10 @@
         <v>4.78</v>
       </c>
       <c r="Q411" t="n">
-        <v>-6.504</v>
+        <v>-6.494</v>
       </c>
       <c r="R411" t="n">
-        <v>-650.4</v>
+        <v>-649.4</v>
       </c>
       <c r="S411" t="n">
         <v>93.2</v>
@@ -32986,10 +32986,10 @@
         <v>3.82</v>
       </c>
       <c r="Q412" t="n">
-        <v>-6.466</v>
+        <v>-6.456</v>
       </c>
       <c r="R412" t="n">
-        <v>-646.6</v>
+        <v>-645.6</v>
       </c>
       <c r="S412" t="n">
         <v>93.2</v>
@@ -33065,10 +33065,10 @@
         <v>4.78</v>
       </c>
       <c r="Q413" t="n">
-        <v>-6.418</v>
+        <v>-6.408</v>
       </c>
       <c r="R413" t="n">
-        <v>-641.8</v>
+        <v>-640.8</v>
       </c>
       <c r="S413" t="n">
         <v>93.2</v>
@@ -33144,10 +33144,10 @@
         <v>-100</v>
       </c>
       <c r="Q414" t="n">
-        <v>-7.418</v>
+        <v>-7.408</v>
       </c>
       <c r="R414" t="n">
-        <v>-741.8</v>
+        <v>-740.8</v>
       </c>
       <c r="S414" t="n">
         <v>93</v>
@@ -33223,10 +33223,10 @@
         <v>3.82</v>
       </c>
       <c r="Q415" t="n">
-        <v>-7.38</v>
+        <v>-7.37</v>
       </c>
       <c r="R415" t="n">
-        <v>-738</v>
+        <v>-737</v>
       </c>
       <c r="S415" t="n">
         <v>93</v>
@@ -33302,10 +33302,10 @@
         <v>3.82</v>
       </c>
       <c r="Q416" t="n">
-        <v>-7.342</v>
+        <v>-7.332</v>
       </c>
       <c r="R416" t="n">
-        <v>-734.2</v>
+        <v>-733.2</v>
       </c>
       <c r="S416" t="n">
         <v>93</v>
@@ -33381,10 +33381,10 @@
         <v>4.78</v>
       </c>
       <c r="Q417" t="n">
-        <v>-7.294</v>
+        <v>-7.284</v>
       </c>
       <c r="R417" t="n">
-        <v>-729.4</v>
+        <v>-728.4</v>
       </c>
       <c r="S417" t="n">
         <v>93</v>
@@ -33460,10 +33460,10 @@
         <v>3.82</v>
       </c>
       <c r="Q418" t="n">
-        <v>-7.256</v>
+        <v>-7.246</v>
       </c>
       <c r="R418" t="n">
-        <v>-725.6</v>
+        <v>-724.6</v>
       </c>
       <c r="S418" t="n">
         <v>93</v>
@@ -33539,10 +33539,10 @@
         <v>3.82</v>
       </c>
       <c r="Q419" t="n">
-        <v>-7.218</v>
+        <v>-7.208</v>
       </c>
       <c r="R419" t="n">
-        <v>-721.8</v>
+        <v>-720.8</v>
       </c>
       <c r="S419" t="n">
         <v>93.09999999999999</v>
@@ -33618,10 +33618,10 @@
         <v>2.87</v>
       </c>
       <c r="Q420" t="n">
-        <v>-7.189</v>
+        <v>-7.179</v>
       </c>
       <c r="R420" t="n">
-        <v>-718.9</v>
+        <v>-717.9</v>
       </c>
       <c r="S420" t="n">
         <v>93.09999999999999</v>
@@ -33697,10 +33697,10 @@
         <v>-100</v>
       </c>
       <c r="Q421" t="n">
-        <v>-8.189</v>
+        <v>-8.179</v>
       </c>
       <c r="R421" t="n">
-        <v>-818.9</v>
+        <v>-817.9</v>
       </c>
       <c r="S421" t="n">
         <v>92.90000000000001</v>
@@ -33776,10 +33776,10 @@
         <v>-100</v>
       </c>
       <c r="Q422" t="n">
-        <v>-9.189</v>
+        <v>-9.179</v>
       </c>
       <c r="R422" t="n">
-        <v>-918.9</v>
+        <v>-917.9</v>
       </c>
       <c r="S422" t="n">
         <v>92.59999999999999</v>
@@ -33855,10 +33855,10 @@
         <v>5.73</v>
       </c>
       <c r="Q423" t="n">
-        <v>-9.132</v>
+        <v>-9.122</v>
       </c>
       <c r="R423" t="n">
-        <v>-913.2</v>
+        <v>-912.2</v>
       </c>
       <c r="S423" t="n">
         <v>92.7</v>
@@ -33934,10 +33934,10 @@
         <v>5.73</v>
       </c>
       <c r="Q424" t="n">
-        <v>-9.074</v>
+        <v>-9.065</v>
       </c>
       <c r="R424" t="n">
-        <v>-907.4</v>
+        <v>-906.5</v>
       </c>
       <c r="S424" t="n">
         <v>92.7</v>
@@ -34013,10 +34013,10 @@
         <v>-100</v>
       </c>
       <c r="Q425" t="n">
-        <v>-10.074</v>
+        <v>-10.065</v>
       </c>
       <c r="R425" t="n">
-        <v>-1007.4</v>
+        <v>-1006.5</v>
       </c>
       <c r="S425" t="n">
         <v>92.5</v>
@@ -34092,10 +34092,10 @@
         <v>4.78</v>
       </c>
       <c r="Q426" t="n">
-        <v>-10.026</v>
+        <v>-10.017</v>
       </c>
       <c r="R426" t="n">
-        <v>-1002.6</v>
+        <v>-1001.7</v>
       </c>
       <c r="S426" t="n">
         <v>92.5</v>
@@ -34171,10 +34171,10 @@
         <v>4.78</v>
       </c>
       <c r="Q427" t="n">
-        <v>-9.978999999999999</v>
+        <v>-9.968999999999999</v>
       </c>
       <c r="R427" t="n">
-        <v>-997.9</v>
+        <v>-996.9</v>
       </c>
       <c r="S427" t="n">
         <v>92.5</v>
@@ -34250,10 +34250,10 @@
         <v>6.69</v>
       </c>
       <c r="Q428" t="n">
-        <v>-9.912000000000001</v>
+        <v>-9.901999999999999</v>
       </c>
       <c r="R428" t="n">
-        <v>-991.2</v>
+        <v>-990.2</v>
       </c>
       <c r="S428" t="n">
         <v>92.5</v>
@@ -34329,10 +34329,10 @@
         <v>5.73</v>
       </c>
       <c r="Q429" t="n">
-        <v>-9.853999999999999</v>
+        <v>-9.845000000000001</v>
       </c>
       <c r="R429" t="n">
-        <v>-985.4</v>
+        <v>-984.5</v>
       </c>
       <c r="S429" t="n">
         <v>92.5</v>
@@ -34408,10 +34408,10 @@
         <v>9.550000000000001</v>
       </c>
       <c r="Q430" t="n">
-        <v>-9.759</v>
+        <v>-9.749000000000001</v>
       </c>
       <c r="R430" t="n">
-        <v>-975.9</v>
+        <v>-974.9</v>
       </c>
       <c r="S430" t="n">
         <v>92.5</v>
@@ -34487,10 +34487,10 @@
         <v>5.73</v>
       </c>
       <c r="Q431" t="n">
-        <v>-9.702</v>
+        <v>-9.692</v>
       </c>
       <c r="R431" t="n">
-        <v>-970.2</v>
+        <v>-969.2</v>
       </c>
       <c r="S431" t="n">
         <v>92.59999999999999</v>
@@ -34566,10 +34566,10 @@
         <v>-100</v>
       </c>
       <c r="Q432" t="n">
-        <v>-10.702</v>
+        <v>-10.692</v>
       </c>
       <c r="R432" t="n">
-        <v>-1070.2</v>
+        <v>-1069.2</v>
       </c>
       <c r="S432" t="n">
         <v>92.3</v>
@@ -34645,10 +34645,10 @@
         <v>6.69</v>
       </c>
       <c r="Q433" t="n">
-        <v>-10.635</v>
+        <v>-10.625</v>
       </c>
       <c r="R433" t="n">
-        <v>-1063.5</v>
+        <v>-1062.5</v>
       </c>
       <c r="S433" t="n">
         <v>92.40000000000001</v>
@@ -34724,10 +34724,10 @@
         <v>3.82</v>
       </c>
       <c r="Q434" t="n">
-        <v>-10.597</v>
+        <v>-10.587</v>
       </c>
       <c r="R434" t="n">
-        <v>-1059.7</v>
+        <v>-1058.7</v>
       </c>
       <c r="S434" t="n">
         <v>92.40000000000001</v>
@@ -34803,10 +34803,10 @@
         <v>3.82</v>
       </c>
       <c r="Q435" t="n">
-        <v>-10.558</v>
+        <v>-10.549</v>
       </c>
       <c r="R435" t="n">
-        <v>-1055.8</v>
+        <v>-1054.9</v>
       </c>
       <c r="S435" t="n">
         <v>92.40000000000001</v>
@@ -34882,10 +34882,10 @@
         <v>9.550000000000001</v>
       </c>
       <c r="Q436" t="n">
-        <v>-10.463</v>
+        <v>-10.453</v>
       </c>
       <c r="R436" t="n">
-        <v>-1046.3</v>
+        <v>-1045.3</v>
       </c>
       <c r="S436" t="n">
         <v>92.40000000000001</v>
@@ -34961,10 +34961,10 @@
         <v>4.78</v>
       </c>
       <c r="Q437" t="n">
-        <v>-10.415</v>
+        <v>-10.405</v>
       </c>
       <c r="R437" t="n">
-        <v>-1041.5</v>
+        <v>-1040.5</v>
       </c>
       <c r="S437" t="n">
         <v>92.40000000000001</v>
@@ -35040,10 +35040,10 @@
         <v>3.82</v>
       </c>
       <c r="Q438" t="n">
-        <v>-10.377</v>
+        <v>-10.367</v>
       </c>
       <c r="R438" t="n">
-        <v>-1037.7</v>
+        <v>-1036.7</v>
       </c>
       <c r="S438" t="n">
         <v>92.40000000000001</v>
@@ -35119,10 +35119,10 @@
         <v>1.91</v>
       </c>
       <c r="Q439" t="n">
-        <v>-10.358</v>
+        <v>-10.348</v>
       </c>
       <c r="R439" t="n">
-        <v>-1035.8</v>
+        <v>-1034.8</v>
       </c>
       <c r="S439" t="n">
         <v>92.5</v>
@@ -35198,10 +35198,10 @@
         <v>2.87</v>
       </c>
       <c r="Q440" t="n">
-        <v>-10.329</v>
+        <v>-10.319</v>
       </c>
       <c r="R440" t="n">
-        <v>-1032.9</v>
+        <v>-1031.9</v>
       </c>
       <c r="S440" t="n">
         <v>92.5</v>
@@ -35277,10 +35277,10 @@
         <v>3.82</v>
       </c>
       <c r="Q441" t="n">
-        <v>-10.291</v>
+        <v>-10.281</v>
       </c>
       <c r="R441" t="n">
-        <v>-1029.1</v>
+        <v>-1028.1</v>
       </c>
       <c r="S441" t="n">
         <v>92.5</v>
@@ -35356,10 +35356,10 @@
         <v>11.46</v>
       </c>
       <c r="Q442" t="n">
-        <v>-10.176</v>
+        <v>-10.167</v>
       </c>
       <c r="R442" t="n">
-        <v>-1017.6</v>
+        <v>-1016.7</v>
       </c>
       <c r="S442" t="n">
         <v>92.5</v>
@@ -35435,10 +35435,10 @@
         <v>5.73</v>
       </c>
       <c r="Q443" t="n">
-        <v>-10.119</v>
+        <v>-10.109</v>
       </c>
       <c r="R443" t="n">
-        <v>-1011.9</v>
+        <v>-1010.9</v>
       </c>
       <c r="S443" t="n">
         <v>92.5</v>
@@ -35514,10 +35514,10 @@
         <v>6.69</v>
       </c>
       <c r="Q444" t="n">
-        <v>-10.052</v>
+        <v>-10.042</v>
       </c>
       <c r="R444" t="n">
-        <v>-1005.2</v>
+        <v>-1004.2</v>
       </c>
       <c r="S444" t="n">
         <v>92.59999999999999</v>
@@ -35593,10 +35593,10 @@
         <v>12.41</v>
       </c>
       <c r="Q445" t="n">
-        <v>-9.928000000000001</v>
+        <v>-9.917999999999999</v>
       </c>
       <c r="R445" t="n">
-        <v>-992.8</v>
+        <v>-991.8</v>
       </c>
       <c r="S445" t="n">
         <v>92.59999999999999</v>
@@ -35672,10 +35672,10 @@
         <v>4.78</v>
       </c>
       <c r="Q446" t="n">
-        <v>-9.880000000000001</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="R446" t="n">
-        <v>-988</v>
+        <v>-987</v>
       </c>
       <c r="S446" t="n">
         <v>92.59999999999999</v>
@@ -35751,10 +35751,10 @@
         <v>3.82</v>
       </c>
       <c r="Q447" t="n">
-        <v>-9.842000000000001</v>
+        <v>-9.832000000000001</v>
       </c>
       <c r="R447" t="n">
-        <v>-984.2</v>
+        <v>-983.2</v>
       </c>
       <c r="S447" t="n">
         <v>92.59999999999999</v>
@@ -35830,10 +35830,10 @@
         <v>5.73</v>
       </c>
       <c r="Q448" t="n">
-        <v>-9.785</v>
+        <v>-9.775</v>
       </c>
       <c r="R448" t="n">
-        <v>-978.5</v>
+        <v>-977.5</v>
       </c>
       <c r="S448" t="n">
         <v>92.59999999999999</v>
@@ -35909,10 +35909,10 @@
         <v>4.78</v>
       </c>
       <c r="Q449" t="n">
-        <v>-9.737</v>
+        <v>-9.727</v>
       </c>
       <c r="R449" t="n">
-        <v>-973.7</v>
+        <v>-972.7</v>
       </c>
       <c r="S449" t="n">
         <v>92.59999999999999</v>
@@ -35988,10 +35988,10 @@
         <v>4.78</v>
       </c>
       <c r="Q450" t="n">
-        <v>-9.689</v>
+        <v>-9.679</v>
       </c>
       <c r="R450" t="n">
-        <v>-968.9</v>
+        <v>-967.9</v>
       </c>
       <c r="S450" t="n">
         <v>92.7</v>
@@ -36067,10 +36067,10 @@
         <v>7.64</v>
       </c>
       <c r="Q451" t="n">
-        <v>-9.613</v>
+        <v>-9.603</v>
       </c>
       <c r="R451" t="n">
-        <v>-961.3</v>
+        <v>-960.3</v>
       </c>
       <c r="S451" t="n">
         <v>92.7</v>
@@ -36146,10 +36146,10 @@
         <v>5.73</v>
       </c>
       <c r="Q452" t="n">
-        <v>-9.555</v>
+        <v>-9.545999999999999</v>
       </c>
       <c r="R452" t="n">
-        <v>-955.5</v>
+        <v>-954.6</v>
       </c>
       <c r="S452" t="n">
         <v>92.7</v>
@@ -36225,10 +36225,10 @@
         <v>5.73</v>
       </c>
       <c r="Q453" t="n">
-        <v>-9.497999999999999</v>
+        <v>-9.488</v>
       </c>
       <c r="R453" t="n">
-        <v>-949.8</v>
+        <v>-948.8</v>
       </c>
       <c r="S453" t="n">
         <v>92.7</v>
@@ -36304,10 +36304,10 @@
         <v>3.82</v>
       </c>
       <c r="Q454" t="n">
-        <v>-9.460000000000001</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="R454" t="n">
-        <v>-946</v>
+        <v>-945</v>
       </c>
       <c r="S454" t="n">
         <v>92.7</v>
@@ -36383,10 +36383,10 @@
         <v>6.69</v>
       </c>
       <c r="Q455" t="n">
-        <v>-9.393000000000001</v>
+        <v>-9.382999999999999</v>
       </c>
       <c r="R455" t="n">
-        <v>-939.3</v>
+        <v>-938.3</v>
       </c>
       <c r="S455" t="n">
         <v>92.7</v>
@@ -36462,10 +36462,10 @@
         <v>5.73</v>
       </c>
       <c r="Q456" t="n">
-        <v>-9.336</v>
+        <v>-9.326000000000001</v>
       </c>
       <c r="R456" t="n">
-        <v>-933.6</v>
+        <v>-932.6</v>
       </c>
       <c r="S456" t="n">
         <v>92.7</v>
@@ -36541,10 +36541,10 @@
         <v>5.73</v>
       </c>
       <c r="Q457" t="n">
-        <v>-9.278</v>
+        <v>-9.269</v>
       </c>
       <c r="R457" t="n">
-        <v>-927.8</v>
+        <v>-926.9</v>
       </c>
       <c r="S457" t="n">
         <v>92.8</v>
@@ -36620,10 +36620,10 @@
         <v>4.78</v>
       </c>
       <c r="Q458" t="n">
-        <v>-9.231</v>
+        <v>-9.221</v>
       </c>
       <c r="R458" t="n">
-        <v>-923.1</v>
+        <v>-922.1</v>
       </c>
       <c r="S458" t="n">
         <v>92.8</v>
@@ -36699,10 +36699,10 @@
         <v>3.82</v>
       </c>
       <c r="Q459" t="n">
-        <v>-9.192</v>
+        <v>-9.183</v>
       </c>
       <c r="R459" t="n">
-        <v>-919.2</v>
+        <v>-918.3</v>
       </c>
       <c r="S459" t="n">
         <v>92.8</v>
@@ -36778,10 +36778,10 @@
         <v>4.78</v>
       </c>
       <c r="Q460" t="n">
-        <v>-9.145</v>
+        <v>-9.135</v>
       </c>
       <c r="R460" t="n">
-        <v>-914.5</v>
+        <v>-913.5</v>
       </c>
       <c r="S460" t="n">
         <v>92.8</v>
@@ -36857,10 +36857,10 @@
         <v>5.73</v>
       </c>
       <c r="Q461" t="n">
-        <v>-9.087</v>
+        <v>-9.077999999999999</v>
       </c>
       <c r="R461" t="n">
-        <v>-908.7</v>
+        <v>-907.8</v>
       </c>
       <c r="S461" t="n">
         <v>92.8</v>
@@ -36936,10 +36936,10 @@
         <v>-100</v>
       </c>
       <c r="Q462" t="n">
-        <v>-10.087</v>
+        <v>-10.078</v>
       </c>
       <c r="R462" t="n">
-        <v>-1008.7</v>
+        <v>-1007.8</v>
       </c>
       <c r="S462" t="n">
         <v>92.59999999999999</v>
@@ -37015,10 +37015,10 @@
         <v>4.78</v>
       </c>
       <c r="Q463" t="n">
-        <v>-10.039</v>
+        <v>-10.03</v>
       </c>
       <c r="R463" t="n">
-        <v>-1003.9</v>
+        <v>-1003</v>
       </c>
       <c r="S463" t="n">
         <v>92.59999999999999</v>
@@ -37094,10 +37094,10 @@
         <v>6.69</v>
       </c>
       <c r="Q464" t="n">
-        <v>-9.973000000000001</v>
+        <v>-9.962999999999999</v>
       </c>
       <c r="R464" t="n">
-        <v>-997.3</v>
+        <v>-996.3</v>
       </c>
       <c r="S464" t="n">
         <v>92.7</v>
@@ -37173,10 +37173,10 @@
         <v>5.73</v>
       </c>
       <c r="Q465" t="n">
-        <v>-9.914999999999999</v>
+        <v>-9.906000000000001</v>
       </c>
       <c r="R465" t="n">
-        <v>-991.5</v>
+        <v>-990.6</v>
       </c>
       <c r="S465" t="n">
         <v>92.7</v>
@@ -37252,10 +37252,10 @@
         <v>7.64</v>
       </c>
       <c r="Q466" t="n">
-        <v>-9.839</v>
+        <v>-9.829000000000001</v>
       </c>
       <c r="R466" t="n">
-        <v>-983.9</v>
+        <v>-982.9</v>
       </c>
       <c r="S466" t="n">
         <v>92.7</v>
@@ -37331,10 +37331,10 @@
         <v>2.87</v>
       </c>
       <c r="Q467" t="n">
-        <v>-9.81</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="R467" t="n">
-        <v>-981</v>
+        <v>-980</v>
       </c>
       <c r="S467" t="n">
         <v>92.7</v>
@@ -37410,10 +37410,10 @@
         <v>5.73</v>
       </c>
       <c r="Q468" t="n">
-        <v>-9.753</v>
+        <v>-9.743</v>
       </c>
       <c r="R468" t="n">
-        <v>-975.3</v>
+        <v>-974.3</v>
       </c>
       <c r="S468" t="n">
         <v>92.7</v>
@@ -37489,10 +37489,10 @@
         <v>2.87</v>
       </c>
       <c r="Q469" t="n">
-        <v>-9.724</v>
+        <v>-9.714</v>
       </c>
       <c r="R469" t="n">
-        <v>-972.4</v>
+        <v>-971.4</v>
       </c>
       <c r="S469" t="n">
         <v>92.7</v>
@@ -37568,10 +37568,10 @@
         <v>3.82</v>
       </c>
       <c r="Q470" t="n">
-        <v>-9.686</v>
+        <v>-9.676</v>
       </c>
       <c r="R470" t="n">
-        <v>-968.6</v>
+        <v>-967.6</v>
       </c>
       <c r="S470" t="n">
         <v>92.8</v>
@@ -37647,10 +37647,10 @@
         <v>2.87</v>
       </c>
       <c r="Q471" t="n">
-        <v>-9.657</v>
+        <v>-9.648</v>
       </c>
       <c r="R471" t="n">
-        <v>-965.7</v>
+        <v>-964.8</v>
       </c>
       <c r="S471" t="n">
         <v>92.8</v>
@@ -37726,13 +37726,2383 @@
         <v>1.91</v>
       </c>
       <c r="Q472" t="n">
-        <v>-9.638</v>
+        <v>-9.628</v>
       </c>
       <c r="R472" t="n">
-        <v>-963.8</v>
+        <v>-962.8</v>
       </c>
       <c r="S472" t="n">
         <v>92.8</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>472</v>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>ARGENTINA 2</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Atl. Rafaela</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Tristan Suarez</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>Atl. Rafaela</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>Tristan Suarez</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="J473" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K473" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M473" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O473" t="n">
+        <v>0.0669</v>
+      </c>
+      <c r="P473" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="Q473" t="n">
+        <v>-9.561999999999999</v>
+      </c>
+      <c r="R473" t="n">
+        <v>-956.2</v>
+      </c>
+      <c r="S473" t="n">
+        <v>92.8</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>473</v>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>ARGENTINA 2</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Def. de Belgrano</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>Def. de Belgrano</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="J474" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K474" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M474" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O474" t="n">
+        <v>0.0573</v>
+      </c>
+      <c r="P474" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="Q474" t="n">
+        <v>-9.504</v>
+      </c>
+      <c r="R474" t="n">
+        <v>-950.4</v>
+      </c>
+      <c r="S474" t="n">
+        <v>92.8</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>474</v>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>SPAIN Primera Rfef Group 2</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Antequera</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>UD Ibiza</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>UD Ibiza</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>Antequera</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="J475" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K475" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M475" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O475" t="n">
+        <v>0.1051</v>
+      </c>
+      <c r="P475" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="Q475" t="n">
+        <v>-9.398999999999999</v>
+      </c>
+      <c r="R475" t="n">
+        <v>-939.9</v>
+      </c>
+      <c r="S475" t="n">
+        <v>92.8</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>475</v>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>BRAZIL 2</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Criciuma</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>Criciuma</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="J476" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K476" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M476" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O476" t="n">
+        <v>0.0955</v>
+      </c>
+      <c r="P476" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="Q476" t="n">
+        <v>-9.304</v>
+      </c>
+      <c r="R476" t="n">
+        <v>-930.4</v>
+      </c>
+      <c r="S476" t="n">
+        <v>92.8</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>476</v>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>SPAIN 1</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="J477" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K477" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M477" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O477" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="P477" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="Q477" t="n">
+        <v>-9.256</v>
+      </c>
+      <c r="R477" t="n">
+        <v>-925.6</v>
+      </c>
+      <c r="S477" t="n">
+        <v>92.90000000000001</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>477</v>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>ARGENTINA 2</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Los Andes</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Acassuso</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>Acassuso</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>Los Andes</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="J478" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="K478" t="n">
+        <v>3</v>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M478" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O478" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="P478" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="Q478" t="n">
+        <v>-9.218</v>
+      </c>
+      <c r="R478" t="n">
+        <v>-921.8</v>
+      </c>
+      <c r="S478" t="n">
+        <v>92.90000000000001</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>478</v>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>EGYPT 1</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Ghazl El Mahallah</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Enppi</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>Enppi</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>Ghazl El Mahallah</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="J479" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K479" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M479" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O479" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="P479" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="Q479" t="n">
+        <v>-9.179</v>
+      </c>
+      <c r="R479" t="n">
+        <v>-917.9</v>
+      </c>
+      <c r="S479" t="n">
+        <v>92.90000000000001</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>479</v>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>EGYPT 1</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>El Gaish</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>ZED</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>El Gaish</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>ZED</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="J480" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K480" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M480" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O480" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="P480" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="Q480" t="n">
+        <v>-9.141</v>
+      </c>
+      <c r="R480" t="n">
+        <v>-914.1</v>
+      </c>
+      <c r="S480" t="n">
+        <v>92.90000000000001</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>480</v>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>EGYPT 1</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Abu Qir Semad</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Al Ittihad</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>Abu Qir Semad</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>Al Ittihad</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="J481" t="n">
+        <v>1</v>
+      </c>
+      <c r="K481" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M481" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O481" t="n">
+        <v>0.0287</v>
+      </c>
+      <c r="P481" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q481" t="n">
+        <v>-9.113</v>
+      </c>
+      <c r="R481" t="n">
+        <v>-911.3</v>
+      </c>
+      <c r="S481" t="n">
+        <v>92.90000000000001</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>481</v>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>BRAZIL 4</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>Goiatuba</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>EC Sao Jose</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>EC Sao Jose</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>Goiatuba</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J482" t="n">
+        <v>1</v>
+      </c>
+      <c r="K482" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M482" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O482" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="P482" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="Q482" t="n">
+        <v>-9.074</v>
+      </c>
+      <c r="R482" t="n">
+        <v>-907.4</v>
+      </c>
+      <c r="S482" t="n">
+        <v>92.90000000000001</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>482</v>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>EGYPT 2</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Al-Sekka</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Maleyeit Kafr El Zayiat</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>Al-Sekka</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>Maleyeit Kafr El Zayiat</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J483" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K483" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M483" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O483" t="n">
+        <v>0.0573</v>
+      </c>
+      <c r="P483" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="Q483" t="n">
+        <v>-9.016999999999999</v>
+      </c>
+      <c r="R483" t="n">
+        <v>-901.7</v>
+      </c>
+      <c r="S483" t="n">
+        <v>92.90000000000001</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>483</v>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>EGYPT 2</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Dayrout</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>WE SC</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>Dayrout</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>WE SC</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="J484" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K484" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M484" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O484" t="n">
+        <v>0.0287</v>
+      </c>
+      <c r="P484" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q484" t="n">
+        <v>-8.988</v>
+      </c>
+      <c r="R484" t="n">
+        <v>-898.8</v>
+      </c>
+      <c r="S484" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>484</v>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>EGYPT 2</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Baladiyat El Mahalla</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Delta United</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>Delta United</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>Baladiyat El Mahalla</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="J485" t="n">
+        <v>1</v>
+      </c>
+      <c r="K485" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M485" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O485" t="n">
+        <v>0.0287</v>
+      </c>
+      <c r="P485" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q485" t="n">
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="R485" t="n">
+        <v>-896</v>
+      </c>
+      <c r="S485" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>485</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>ECUADOR 2</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Atletico FC</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Nueve de Octubre</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>Nueve de Octubre</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>Atletico FC</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="J486" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K486" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M486" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O486" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="P486" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="Q486" t="n">
+        <v>-8.920999999999999</v>
+      </c>
+      <c r="R486" t="n">
+        <v>-892.1</v>
+      </c>
+      <c r="S486" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>486</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>ARGENTINA 2</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Tristan Suarez</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>San Martin T.</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>San Martin T.</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>Tristan Suarez</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="J487" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K487" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M487" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O487" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="P487" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="Q487" t="n">
+        <v>-8.882999999999999</v>
+      </c>
+      <c r="R487" t="n">
+        <v>-888.3</v>
+      </c>
+      <c r="S487" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>487</v>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>ARGENTINA 2</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Acassuso</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>All Boys</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>Acassuso</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>All Boys</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="J488" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K488" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M488" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O488" t="n">
+        <v>0.0669</v>
+      </c>
+      <c r="P488" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="Q488" t="n">
+        <v>-8.816000000000001</v>
+      </c>
+      <c r="R488" t="n">
+        <v>-881.6</v>
+      </c>
+      <c r="S488" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>488</v>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>BRAZIL 3</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Floresta EC</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Maringa FC</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>Floresta EC</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>Maringa FC</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="J489" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K489" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M489" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O489" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="P489" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="Q489" t="n">
+        <v>-8.769</v>
+      </c>
+      <c r="R489" t="n">
+        <v>-876.9</v>
+      </c>
+      <c r="S489" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>489</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>ARGENTINA 2</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Central Norte</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>Central Norte</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="J490" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K490" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M490" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O490" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="P490" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="Q490" t="n">
+        <v>-8.73</v>
+      </c>
+      <c r="R490" t="n">
+        <v>-873</v>
+      </c>
+      <c r="S490" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>490</v>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>EGYPT 1</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>Al Qanah</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>El Gaish</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>Al Qanah</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>El Gaish</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J491" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K491" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M491" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O491" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="P491" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="Q491" t="n">
+        <v>-8.692</v>
+      </c>
+      <c r="R491" t="n">
+        <v>-869.2</v>
+      </c>
+      <c r="S491" t="n">
+        <v>93.09999999999999</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>491</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>SPAIN 1</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J492" t="n">
+        <v>1</v>
+      </c>
+      <c r="K492" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M492" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O492" t="n">
+        <v>0.0764</v>
+      </c>
+      <c r="P492" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="Q492" t="n">
+        <v>-8.616</v>
+      </c>
+      <c r="R492" t="n">
+        <v>-861.6</v>
+      </c>
+      <c r="S492" t="n">
+        <v>93.09999999999999</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>492</v>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>EGYPT 1</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>Smouha</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Ceramica Cleopatra</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>Smouha</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>Ceramica Cleopatra</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="J493" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K493" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M493" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O493" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="P493" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="Q493" t="n">
+        <v>-8.577999999999999</v>
+      </c>
+      <c r="R493" t="n">
+        <v>-857.8</v>
+      </c>
+      <c r="S493" t="n">
+        <v>93.09999999999999</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>493</v>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>COPA SUDAMERICANA</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Santa Fe (COL)</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Vasco (BRA)</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>Vasco (BRA)</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>Santa Fe (COL)</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="J494" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K494" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M494" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O494" t="n">
+        <v>0.0573</v>
+      </c>
+      <c r="P494" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="Q494" t="n">
+        <v>-8.52</v>
+      </c>
+      <c r="R494" t="n">
+        <v>-852</v>
+      </c>
+      <c r="S494" t="n">
+        <v>93.09999999999999</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>494</v>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>EGYPT 1</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>Enppi</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>ZED</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>Enppi</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>ZED</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="J495" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K495" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M495" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O495" t="n">
+        <v>0.0287</v>
+      </c>
+      <c r="P495" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q495" t="n">
+        <v>-8.492000000000001</v>
+      </c>
+      <c r="R495" t="n">
+        <v>-849.2</v>
+      </c>
+      <c r="S495" t="n">
+        <v>93.09999999999999</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>495</v>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>COPA LIBERTADORES</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Estudiantes L.P. (ARG)</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Corinthians (BRA)</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>Corinthians (BRA)</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>Estudiantes L.P. (ARG)</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J496" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K496" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M496" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O496" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="P496" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="Q496" t="n">
+        <v>-8.444000000000001</v>
+      </c>
+      <c r="R496" t="n">
+        <v>-844.4</v>
+      </c>
+      <c r="S496" t="n">
+        <v>93.09999999999999</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>496</v>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>ECUADOR 2</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Cumbaya</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>Gualaceo</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>Gualaceo</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>Cumbaya</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="J497" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K497" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M497" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O497" t="n">
+        <v>0.0573</v>
+      </c>
+      <c r="P497" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="Q497" t="n">
+        <v>-8.385999999999999</v>
+      </c>
+      <c r="R497" t="n">
+        <v>-838.6</v>
+      </c>
+      <c r="S497" t="n">
+        <v>93.09999999999999</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>497</v>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>BRAZIL 2</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Vila Nova FC</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Goias</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>Goias</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>Vila Nova FC</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="J498" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K498" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M498" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O498" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="P498" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="Q498" t="n">
+        <v>-8.339</v>
+      </c>
+      <c r="R498" t="n">
+        <v>-833.9</v>
+      </c>
+      <c r="S498" t="n">
+        <v>93.2</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>498</v>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>EGYPT 2</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>Maleyeit Kafr El Zayiat</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>La Viena</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>La Viena</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>Maleyeit Kafr El Zayiat</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="J499" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K499" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M499" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O499" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="P499" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="Q499" t="n">
+        <v>-8.291</v>
+      </c>
+      <c r="R499" t="n">
+        <v>-829.1</v>
+      </c>
+      <c r="S499" t="n">
+        <v>93.2</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>499</v>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>ECUADOR 2</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>LDU Portoviejo</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>Dep. Santo Domingo</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>Dep. Santo Domingo</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>LDU Portoviejo</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="J500" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K500" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M500" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O500" t="n">
+        <v>0.0573</v>
+      </c>
+      <c r="P500" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="Q500" t="n">
+        <v>-8.234</v>
+      </c>
+      <c r="R500" t="n">
+        <v>-823.4</v>
+      </c>
+      <c r="S500" t="n">
+        <v>93.2</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>500</v>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>JAPAN 2</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>Blaublitz</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Tokushima</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>Tokushima</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>Blaublitz</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="J501" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K501" t="n">
+        <v>3</v>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M501" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O501" t="n">
+        <v>0.1051</v>
+      </c>
+      <c r="P501" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="Q501" t="n">
+        <v>-8.128</v>
+      </c>
+      <c r="R501" t="n">
+        <v>-812.8</v>
+      </c>
+      <c r="S501" t="n">
+        <v>93.2</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>501</v>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>JAPAN 1</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Shimizu S-Pulse</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>Avispa Fukuoka</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>Shimizu S-Pulse</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>Avispa Fukuoka</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="J502" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="K502" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>Favorito EH +2</t>
+        </is>
+      </c>
+      <c r="M502" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="O502" t="n">
+        <v>0.1051</v>
+      </c>
+      <c r="P502" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="Q502" t="n">
+        <v>-8.023</v>
+      </c>
+      <c r="R502" t="n">
+        <v>-802.3</v>
+      </c>
+      <c r="S502" t="n">
+        <v>93.2</v>
       </c>
     </row>
   </sheetData>
@@ -37746,7 +40116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37806,25 +40176,25 @@
         <v>62</v>
       </c>
       <c r="C2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>93.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F2" t="n">
         <v>1.059</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.76</v>
+        <v>-1.83</v>
       </c>
       <c r="H2" t="n">
-        <v>-76.11</v>
+        <v>-182.8</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.2</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="3">
@@ -37899,25 +40269,25 @@
         <v>60</v>
       </c>
       <c r="C5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="F5" t="n">
         <v>1.053</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.26</v>
+        <v>-2.19</v>
       </c>
       <c r="H5" t="n">
-        <v>-325.75</v>
+        <v>-219.05</v>
       </c>
       <c r="I5" t="n">
-        <v>-5.4</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="6">
@@ -37942,10 +40312,10 @@
         <v>1.058</v>
       </c>
       <c r="G6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="H6" t="n">
-        <v>133.4</v>
+        <v>134.36</v>
       </c>
       <c r="I6" t="n">
         <v>2.2</v>
@@ -38020,28 +40390,59 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D9" t="n">
         <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>91.09999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>1.089</v>
+        <v>1.088</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3</v>
+        <v>-1.89</v>
       </c>
       <c r="H9" t="n">
-        <v>-229.64</v>
+        <v>-188.56</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.1</v>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>24</v>
+      </c>
+      <c r="C10" t="n">
+        <v>24</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.052</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H10" t="n">
+        <v>119.43</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
